--- a/fund_tracker/Inputs/Daily_NAV.xlsx
+++ b/fund_tracker/Inputs/Daily_NAV.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8261f3b7260beb32/Documents/Emkay Analytics Tool/fund_tracker/Inputs/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_652E0111CD51562EBAFF31D2F8375B068495DDBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44319461-EFF2-4018-89B7-FC90EAD233E7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -34,29 +28,21 @@
     <t>Benchmark NAV</t>
   </si>
   <si>
-    <t>ABCD01</t>
+    <t>CBTWRR</t>
   </si>
   <si>
-    <t>CBAIFMF</t>
+    <t>ABCD01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -72,7 +58,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -80,30 +66,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -111,25 +79,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -167,7 +123,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -201,7 +157,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -236,10 +191,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -412,204 +366,198 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D495"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="22.21875" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" customWidth="1"/>
-    <col min="4" max="4" width="19.21875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:4">
+      <c r="A2" s="1">
         <v>45869</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>99.363200000000006</v>
+        <v>99.36320000000001</v>
       </c>
       <c r="D2">
-        <v>99.860900000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+        <v>99.8609</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1">
         <v>45870</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>99.658100000000005</v>
+        <v>99.6581</v>
       </c>
       <c r="D3">
         <v>100.0946</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+    <row r="4" spans="1:4">
+      <c r="A4" s="1">
         <v>45873</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>99.417699999999996</v>
+        <v>99.4177</v>
       </c>
       <c r="D4">
         <v>100.276</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+    <row r="5" spans="1:4">
+      <c r="A5" s="1">
         <v>45874</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>99.264899999999997</v>
+        <v>99.2649</v>
       </c>
       <c r="D5">
-        <v>99.446200000000005</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+        <v>99.4462</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1">
         <v>45875</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>99.444599999999994</v>
+        <v>99.44459999999999</v>
       </c>
       <c r="D6">
-        <v>99.558000000000007</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+        <v>99.55800000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1">
         <v>45876</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>99.932199999999995</v>
+        <v>99.93219999999999</v>
       </c>
       <c r="D7">
-        <v>99.779600000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+        <v>99.7796</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1">
         <v>45877</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>99.739500000000007</v>
+        <v>99.73950000000001</v>
       </c>
       <c r="D8">
-        <v>101.82899999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+        <v>101.829</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1">
         <v>45880</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>100.54470000000001</v>
+        <v>100.5447</v>
       </c>
       <c r="D9">
-        <v>103.39870000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+        <v>103.3987</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1">
         <v>45881</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>99.775499999999994</v>
+        <v>99.77549999999999</v>
       </c>
       <c r="D10">
         <v>102.7343</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+    <row r="11" spans="1:4">
+      <c r="A11" s="1">
         <v>45882</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>99.828900000000004</v>
+        <v>99.8289</v>
       </c>
       <c r="D11">
-        <v>102.53919999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+        <v>102.5392</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1">
         <v>45883</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>101.72620000000001</v>
+        <v>101.7262</v>
       </c>
       <c r="D12">
         <v>101.3797</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+    <row r="13" spans="1:4">
+      <c r="A13" s="1">
         <v>45884</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13">
         <v>101.9378</v>
       </c>
       <c r="D13">
-        <v>100.94119999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+        <v>100.9412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1">
         <v>45887</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14">
         <v>103.0291</v>
@@ -618,12 +566,12 @@
         <v>101.2364</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+    <row r="15" spans="1:4">
+      <c r="A15" s="1">
         <v>45888</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>103.1467</v>
@@ -632,600 +580,600 @@
         <v>102.2535</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+    <row r="16" spans="1:4">
+      <c r="A16" s="1">
         <v>45889</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16">
         <v>103.6242</v>
       </c>
       <c r="D16">
-        <v>101.69799999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+        <v>101.698</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1">
         <v>45890</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>103.633</v>
       </c>
       <c r="D17">
-        <v>101.20650000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+        <v>101.2065</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1">
         <v>45891</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18">
         <v>103.5579</v>
       </c>
       <c r="D18">
-        <v>99.508399999999995</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
+        <v>99.50839999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1">
         <v>45894</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19">
-        <v>103.03319999999999</v>
+        <v>103.0332</v>
       </c>
       <c r="D19">
-        <v>99.418700000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
+        <v>99.4187</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1">
         <v>45895</v>
       </c>
       <c r="B20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20">
         <v>103.3997</v>
       </c>
       <c r="D20">
-        <v>98.613500000000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+        <v>98.6135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1">
         <v>45896</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21">
         <v>102.8227</v>
       </c>
       <c r="D21">
-        <v>98.235299999999995</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+        <v>98.2353</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1">
         <v>45897</v>
       </c>
       <c r="B22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22">
         <v>103.3609</v>
       </c>
       <c r="D22">
-        <v>97.585400000000007</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
+        <v>97.58540000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1">
         <v>45898</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23">
         <v>104.2111</v>
       </c>
       <c r="D23">
-        <v>97.550899999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
+        <v>97.5509</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1">
         <v>45901</v>
       </c>
       <c r="B24" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24">
-        <v>104.53440000000001</v>
+        <v>104.5344</v>
       </c>
       <c r="D24">
-        <v>96.218199999999996</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
+        <v>96.2182</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1">
         <v>45902</v>
       </c>
       <c r="B25" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25">
         <v>104.3723</v>
       </c>
       <c r="D25">
-        <v>95.127399999999994</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
+        <v>95.12739999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1">
         <v>45903</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26">
         <v>104.7611</v>
       </c>
       <c r="D26">
-        <v>96.785899999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
+        <v>96.7859</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1">
         <v>45904</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27">
         <v>104.5819</v>
       </c>
       <c r="D27">
-        <v>95.827699999999993</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
+        <v>95.82769999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1">
         <v>45905</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <v>105.3305</v>
       </c>
       <c r="D28">
-        <v>95.025199999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
+        <v>95.0252</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1">
         <v>45908</v>
       </c>
       <c r="B29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29">
-        <v>104.00709999999999</v>
+        <v>104.0071</v>
       </c>
       <c r="D29">
-        <v>96.459699999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
+        <v>96.4597</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1">
         <v>45909</v>
       </c>
       <c r="B30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30">
         <v>103.8092</v>
       </c>
       <c r="D30">
-        <v>98.74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
+        <v>98.73999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1">
         <v>45910</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31">
         <v>102.3869</v>
       </c>
       <c r="D31">
-        <v>97.854100000000003</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
+        <v>97.8541</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1">
         <v>45911</v>
       </c>
       <c r="B32" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32">
         <v>101.346</v>
       </c>
       <c r="D32">
-        <v>97.605000000000004</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
+        <v>97.605</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1">
         <v>45912</v>
       </c>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>102.38079999999999</v>
+        <v>102.3808</v>
       </c>
       <c r="D33">
-        <v>97.910700000000006</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
+        <v>97.91070000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1">
         <v>45915</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34">
         <v>103.0842</v>
       </c>
       <c r="D34">
-        <v>99.303899999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
+        <v>99.3039</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1">
         <v>45916</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35">
         <v>102.6061</v>
       </c>
       <c r="D35">
-        <v>98.559700000000007</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
+        <v>98.55970000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="1">
         <v>45917</v>
       </c>
       <c r="B36" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36">
         <v>101.5574</v>
       </c>
       <c r="D36">
-        <v>98.405699999999996</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
+        <v>98.4057</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1">
         <v>45918</v>
       </c>
       <c r="B37" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>99.461100000000002</v>
+        <v>99.4611</v>
       </c>
       <c r="D37">
-        <v>99.057000000000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
+        <v>99.057</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1">
         <v>45919</v>
       </c>
       <c r="B38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>99.124499999999998</v>
+        <v>99.1245</v>
       </c>
       <c r="D38">
-        <v>99.441199999999995</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
+        <v>99.44119999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1">
         <v>45922</v>
       </c>
       <c r="B39" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39">
         <v>100.8832</v>
       </c>
       <c r="D39">
-        <v>99.181700000000006</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
+        <v>99.18170000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1">
         <v>45923</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40">
         <v>101.2453</v>
       </c>
       <c r="D40">
-        <v>99.115200000000002</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
+        <v>99.1152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1">
         <v>45924</v>
       </c>
       <c r="B41" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41">
-        <v>100.89109999999999</v>
+        <v>100.8911</v>
       </c>
       <c r="D41">
-        <v>98.064599999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
+        <v>98.0646</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1">
         <v>45925</v>
       </c>
       <c r="B42" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42">
         <v>101.2749</v>
       </c>
       <c r="D42">
-        <v>97.917000000000002</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
+        <v>97.917</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1">
         <v>45926</v>
       </c>
       <c r="B43" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>100.1977</v>
       </c>
       <c r="D43">
-        <v>97.747500000000002</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
+        <v>97.7475</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1">
         <v>45929</v>
       </c>
       <c r="B44" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44">
-        <v>100.03440000000001</v>
+        <v>100.0344</v>
       </c>
       <c r="D44">
-        <v>97.968199999999996</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
+        <v>97.9682</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1">
         <v>45930</v>
       </c>
       <c r="B45" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C45">
-        <v>100.15430000000001</v>
+        <v>100.1543</v>
       </c>
       <c r="D45">
-        <v>97.572100000000006</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
+        <v>97.57210000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="1">
         <v>45931</v>
       </c>
       <c r="B46" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C46">
-        <v>100.14190000000001</v>
+        <v>100.1419</v>
       </c>
       <c r="D46">
-        <v>97.979200000000006</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
+        <v>97.97920000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="1">
         <v>45932</v>
       </c>
       <c r="B47" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C47">
-        <v>100.75539999999999</v>
+        <v>100.7554</v>
       </c>
       <c r="D47">
-        <v>98.812200000000004</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
+        <v>98.8122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1">
         <v>45933</v>
       </c>
       <c r="B48" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C48">
         <v>101.0523</v>
       </c>
       <c r="D48">
-        <v>98.974599999999995</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
+        <v>98.9746</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1">
         <v>45936</v>
       </c>
       <c r="B49" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49">
         <v>101.5831</v>
       </c>
       <c r="D49">
-        <v>99.292699999999996</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
+        <v>99.2927</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1">
         <v>45937</v>
       </c>
       <c r="B50" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50">
         <v>101.1344</v>
       </c>
       <c r="D50">
-        <v>99.374700000000004</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
+        <v>99.3747</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="1">
         <v>45938</v>
       </c>
       <c r="B51" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C51">
         <v>101.8312</v>
       </c>
       <c r="D51">
-        <v>99.414500000000004</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2">
+        <v>99.4145</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="1">
         <v>45939</v>
       </c>
       <c r="B52" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C52">
         <v>103.0634</v>
       </c>
       <c r="D52">
-        <v>98.880399999999995</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="2">
+        <v>98.88039999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="1">
         <v>45940</v>
       </c>
       <c r="B53" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C53">
         <v>102.4012</v>
       </c>
       <c r="D53">
-        <v>99.170299999999997</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="2">
+        <v>99.1703</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1">
         <v>45943</v>
       </c>
       <c r="B54" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54">
         <v>101.8034</v>
       </c>
       <c r="D54">
-        <v>99.132800000000003</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="2">
+        <v>99.1328</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1">
         <v>45944</v>
       </c>
       <c r="B55" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C55">
-        <v>102.82250000000001</v>
+        <v>102.8225</v>
       </c>
       <c r="D55">
-        <v>100.83240000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="2">
+        <v>100.8324</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1">
         <v>45945</v>
       </c>
       <c r="B56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C56">
-        <v>102.73260000000001</v>
+        <v>102.7326</v>
       </c>
       <c r="D56">
-        <v>102.14190000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
+        <v>102.1419</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1">
         <v>45946</v>
       </c>
       <c r="B57" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C57">
         <v>103.8109</v>
       </c>
       <c r="D57">
-        <v>102.49809999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="2">
+        <v>102.4981</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="1">
         <v>45947</v>
       </c>
       <c r="B58" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C58">
         <v>103.5343</v>
@@ -1234,12 +1182,12 @@
         <v>101.9134</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="2">
+    <row r="59" spans="1:4">
+      <c r="A59" s="1">
         <v>45950</v>
       </c>
       <c r="B59" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C59">
         <v>104.6588</v>
@@ -1248,12 +1196,12 @@
         <v>101.0472</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="2">
+    <row r="60" spans="1:4">
+      <c r="A60" s="1">
         <v>45951</v>
       </c>
       <c r="B60" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C60">
         <v>104.8081</v>
@@ -1262,96 +1210,96 @@
         <v>102.0505</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="2">
+    <row r="61" spans="1:4">
+      <c r="A61" s="1">
         <v>45952</v>
       </c>
       <c r="B61" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C61">
-        <v>105.05240000000001</v>
+        <v>105.0524</v>
       </c>
       <c r="D61">
         <v>102.3058</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="2">
+    <row r="62" spans="1:4">
+      <c r="A62" s="1">
         <v>45953</v>
       </c>
       <c r="B62" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C62">
-        <v>106.27549999999999</v>
+        <v>106.2755</v>
       </c>
       <c r="D62">
         <v>102.7397</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="2">
+    <row r="63" spans="1:4">
+      <c r="A63" s="1">
         <v>45954</v>
       </c>
       <c r="B63" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C63">
         <v>106.0535</v>
       </c>
       <c r="D63">
-        <v>101.34690000000001</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="2">
+        <v>101.3469</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="1">
         <v>45957</v>
       </c>
       <c r="B64" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C64">
-        <v>105.39400000000001</v>
+        <v>105.394</v>
       </c>
       <c r="D64">
-        <v>102.13939999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="2">
+        <v>102.1394</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="1">
         <v>45958</v>
       </c>
       <c r="B65" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65">
         <v>105.1086</v>
       </c>
       <c r="D65">
-        <v>102.55159999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="2">
+        <v>102.5516</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="1">
         <v>45959</v>
       </c>
       <c r="B66" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C66">
-        <v>105.49890000000001</v>
+        <v>105.4989</v>
       </c>
       <c r="D66">
         <v>101.6816</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="2">
+    <row r="67" spans="1:4">
+      <c r="A67" s="1">
         <v>45960</v>
       </c>
       <c r="B67" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C67">
         <v>104.3732</v>
@@ -1360,12 +1308,12 @@
         <v>101.3387</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="2">
+    <row r="68" spans="1:4">
+      <c r="A68" s="1">
         <v>45961</v>
       </c>
       <c r="B68" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68">
         <v>104.8985</v>
@@ -1374,12 +1322,12 @@
         <v>101.593</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="2">
+    <row r="69" spans="1:4">
+      <c r="A69" s="1">
         <v>45964</v>
       </c>
       <c r="B69" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C69">
         <v>104.547</v>
@@ -1388,26 +1336,26 @@
         <v>101.6763</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="2">
+    <row r="70" spans="1:4">
+      <c r="A70" s="1">
         <v>45965</v>
       </c>
       <c r="B70" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C70">
-        <v>105.45359999999999</v>
+        <v>105.4536</v>
       </c>
       <c r="D70">
-        <v>101.47929999999999</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="2">
+        <v>101.4793</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="1">
         <v>45966</v>
       </c>
       <c r="B71" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C71">
         <v>103.7055</v>
@@ -1416,26 +1364,26 @@
         <v>101.4359</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="2">
+    <row r="72" spans="1:4">
+      <c r="A72" s="1">
         <v>45967</v>
       </c>
       <c r="B72" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C72">
-        <v>103.17489999999999</v>
+        <v>103.1749</v>
       </c>
       <c r="D72">
-        <v>101.27200000000001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="2">
+        <v>101.272</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="1">
         <v>45968</v>
       </c>
       <c r="B73" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C73">
         <v>101.9851</v>
@@ -1444,12 +1392,12 @@
         <v>101.4361</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="2">
+    <row r="74" spans="1:4">
+      <c r="A74" s="1">
         <v>45971</v>
       </c>
       <c r="B74" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C74">
         <v>101.4344</v>
@@ -1458,12 +1406,12 @@
         <v>102.6708</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="2">
+    <row r="75" spans="1:4">
+      <c r="A75" s="1">
         <v>45972</v>
       </c>
       <c r="B75" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C75">
         <v>101.6632</v>
@@ -1472,12 +1420,12 @@
         <v>100.6037</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="2">
+    <row r="76" spans="1:4">
+      <c r="A76" s="1">
         <v>45973</v>
       </c>
       <c r="B76" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76">
         <v>101.5831</v>
@@ -1486,12 +1434,12 @@
         <v>100.4533</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="2">
+    <row r="77" spans="1:4">
+      <c r="A77" s="1">
         <v>45974</v>
       </c>
       <c r="B77" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77">
         <v>101.4494</v>
@@ -1500,12 +1448,12 @@
         <v>100.6353</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="2">
+    <row r="78" spans="1:4">
+      <c r="A78" s="1">
         <v>45975</v>
       </c>
       <c r="B78" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C78">
         <v>101.3839</v>
@@ -1514,12 +1462,12 @@
         <v>100.9139</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="2">
+    <row r="79" spans="1:4">
+      <c r="A79" s="1">
         <v>45978</v>
       </c>
       <c r="B79" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C79">
         <v>101.5805</v>
@@ -1528,40 +1476,40 @@
         <v>100.654</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="2">
+    <row r="80" spans="1:4">
+      <c r="A80" s="1">
         <v>45979</v>
       </c>
       <c r="B80" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C80">
         <v>100.9</v>
       </c>
       <c r="D80">
-        <v>99.279700000000005</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="2">
+        <v>99.27970000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="1">
         <v>45980</v>
       </c>
       <c r="B81" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C81">
-        <v>101.45780000000001</v>
+        <v>101.4578</v>
       </c>
       <c r="D81">
-        <v>99.579899999999995</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="2">
+        <v>99.57989999999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="1">
         <v>45981</v>
       </c>
       <c r="B82" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C82">
         <v>101.9867</v>
@@ -1570,26 +1518,26 @@
         <v>100.9958</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="2">
+    <row r="83" spans="1:4">
+      <c r="A83" s="1">
         <v>45982</v>
       </c>
       <c r="B83" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C83">
-        <v>102.31659999999999</v>
+        <v>102.3166</v>
       </c>
       <c r="D83">
-        <v>99.796899999999994</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="2">
+        <v>99.79689999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="1">
         <v>45985</v>
       </c>
       <c r="B84" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C84">
         <v>102.7726</v>
@@ -1598,96 +1546,96 @@
         <v>100.5265</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="2">
+    <row r="85" spans="1:4">
+      <c r="A85" s="1">
         <v>45986</v>
       </c>
       <c r="B85" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C85">
         <v>103.04</v>
       </c>
       <c r="D85">
-        <v>100.30249999999999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="2">
+        <v>100.3025</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="1">
         <v>45987</v>
       </c>
       <c r="B86" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C86">
         <v>104.5852</v>
       </c>
       <c r="D86">
-        <v>100.29340000000001</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="2">
+        <v>100.2934</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="1">
         <v>45988</v>
       </c>
       <c r="B87" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C87">
         <v>104.5715</v>
       </c>
       <c r="D87">
-        <v>99.488699999999994</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="2">
+        <v>99.48869999999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="1">
         <v>45989</v>
       </c>
       <c r="B88" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C88">
         <v>104.3938</v>
       </c>
       <c r="D88">
-        <v>99.262299999999996</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="2">
+        <v>99.2623</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="1">
         <v>45992</v>
       </c>
       <c r="B89" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C89">
-        <v>103.88420000000001</v>
+        <v>103.8842</v>
       </c>
       <c r="D89">
         <v>100.3344</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="2">
+    <row r="90" spans="1:4">
+      <c r="A90" s="1">
         <v>45993</v>
       </c>
       <c r="B90" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C90">
         <v>103.1707</v>
       </c>
       <c r="D90">
-        <v>100.84220000000001</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="2">
+        <v>100.8422</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="1">
         <v>45994</v>
       </c>
       <c r="B91" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C91">
         <v>102.306</v>
@@ -1696,68 +1644,68 @@
         <v>102.2801</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
+    <row r="92" spans="1:4">
+      <c r="A92" s="1">
         <v>45995</v>
       </c>
       <c r="B92" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C92">
         <v>101.708</v>
       </c>
       <c r="D92">
-        <v>103.28440000000001</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="2">
+        <v>103.2844</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="1">
         <v>45996</v>
       </c>
       <c r="B93" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C93">
-        <v>101.70650000000001</v>
+        <v>101.7065</v>
       </c>
       <c r="D93">
         <v>103.6885</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="2">
+    <row r="94" spans="1:4">
+      <c r="A94" s="1">
         <v>45999</v>
       </c>
       <c r="B94" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C94">
         <v>101.9987</v>
       </c>
       <c r="D94">
-        <v>105.17659999999999</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="2">
+        <v>105.1766</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="1">
         <v>46000</v>
       </c>
       <c r="B95" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C95">
-        <v>102.08580000000001</v>
+        <v>102.0858</v>
       </c>
       <c r="D95">
-        <v>105.58799999999999</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="2">
+        <v>105.588</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="1">
         <v>46001</v>
       </c>
       <c r="B96" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C96">
         <v>101.5787</v>
@@ -1766,26 +1714,26 @@
         <v>106.3297</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="2">
+    <row r="97" spans="1:4">
+      <c r="A97" s="1">
         <v>46002</v>
       </c>
       <c r="B97" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C97">
-        <v>102.28019999999999</v>
+        <v>102.2802</v>
       </c>
       <c r="D97">
         <v>106.1199</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="2">
+    <row r="98" spans="1:4">
+      <c r="A98" s="1">
         <v>46003</v>
       </c>
       <c r="B98" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C98">
         <v>102.8694</v>
@@ -1794,12 +1742,12 @@
         <v>106.2189</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="2">
+    <row r="99" spans="1:4">
+      <c r="A99" s="1">
         <v>46006</v>
       </c>
       <c r="B99" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C99">
         <v>102.8027</v>
@@ -1808,12 +1756,12 @@
         <v>105.6687</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="2">
+    <row r="100" spans="1:4">
+      <c r="A100" s="1">
         <v>46007</v>
       </c>
       <c r="B100" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C100">
         <v>102.3746</v>
@@ -1822,68 +1770,68 @@
         <v>106.5475</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="2">
+    <row r="101" spans="1:4">
+      <c r="A101" s="1">
         <v>46008</v>
       </c>
       <c r="B101" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C101">
         <v>102.8249</v>
       </c>
       <c r="D101">
-        <v>105.58580000000001</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="2">
+        <v>105.5858</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="1">
         <v>46009</v>
       </c>
       <c r="B102" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C102">
-        <v>103.01300000000001</v>
+        <v>103.013</v>
       </c>
       <c r="D102">
         <v>106.2889</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="2">
+    <row r="103" spans="1:4">
+      <c r="A103" s="1">
         <v>46010</v>
       </c>
       <c r="B103" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C103">
-        <v>102.00020000000001</v>
+        <v>102.0002</v>
       </c>
       <c r="D103">
-        <v>106.16930000000001</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="2">
+        <v>106.1693</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="1">
         <v>46013</v>
       </c>
       <c r="B104" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C104">
-        <v>102.00069999999999</v>
+        <v>102.0007</v>
       </c>
       <c r="D104">
-        <v>107.20650000000001</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="2">
+        <v>107.2065</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="1">
         <v>46014</v>
       </c>
       <c r="B105" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C105">
         <v>102.2411</v>
@@ -1892,26 +1840,26 @@
         <v>107.8934</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="2">
+    <row r="106" spans="1:4">
+      <c r="A106" s="1">
         <v>46015</v>
       </c>
       <c r="B106" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C106">
-        <v>101.63549999999999</v>
+        <v>101.6355</v>
       </c>
       <c r="D106">
         <v>109.5081</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="2">
+    <row r="107" spans="1:4">
+      <c r="A107" s="1">
         <v>46016</v>
       </c>
       <c r="B107" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C107">
         <v>101.8228</v>
@@ -1920,12 +1868,12 @@
         <v>110.1921</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="2">
+    <row r="108" spans="1:4">
+      <c r="A108" s="1">
         <v>46017</v>
       </c>
       <c r="B108" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C108">
         <v>100.8168</v>
@@ -1934,26 +1882,26 @@
         <v>108.8503</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="2">
+    <row r="109" spans="1:4">
+      <c r="A109" s="1">
         <v>46020</v>
       </c>
       <c r="B109" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C109">
-        <v>101.82640000000001</v>
+        <v>101.8264</v>
       </c>
       <c r="D109">
         <v>108.8356</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="2">
+    <row r="110" spans="1:4">
+      <c r="A110" s="1">
         <v>46021</v>
       </c>
       <c r="B110" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C110">
         <v>102.782</v>
@@ -1962,12 +1910,12 @@
         <v>107.8586</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="2">
+    <row r="111" spans="1:4">
+      <c r="A111" s="1">
         <v>46022</v>
       </c>
       <c r="B111" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C111">
         <v>102.6473</v>
@@ -1976,12 +1924,12 @@
         <v>107.4546</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="2">
+    <row r="112" spans="1:4">
+      <c r="A112" s="1">
         <v>46023</v>
       </c>
       <c r="B112" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C112">
         <v>102.9635</v>
@@ -1990,12 +1938,12 @@
         <v>108.7967</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="2">
+    <row r="113" spans="1:4">
+      <c r="A113" s="1">
         <v>46024</v>
       </c>
       <c r="B113" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C113">
         <v>101.2453</v>
@@ -2004,12 +1952,12 @@
         <v>109.3951</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="2">
+    <row r="114" spans="1:4">
+      <c r="A114" s="1">
         <v>46027</v>
       </c>
       <c r="B114" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C114">
         <v>100.4603</v>
@@ -2018,12 +1966,12 @@
         <v>108.8272</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="2">
+    <row r="115" spans="1:4">
+      <c r="A115" s="1">
         <v>46028</v>
       </c>
       <c r="B115" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C115">
         <v>100.2991</v>
@@ -2032,40 +1980,40 @@
         <v>107.9881</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="2">
+    <row r="116" spans="1:4">
+      <c r="A116" s="1">
         <v>46029</v>
       </c>
       <c r="B116" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C116">
-        <v>99.581800000000001</v>
+        <v>99.5818</v>
       </c>
       <c r="D116">
-        <v>108.05970000000001</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="2">
+        <v>108.0597</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="1">
         <v>46030</v>
       </c>
       <c r="B117" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C117">
-        <v>100.13760000000001</v>
+        <v>100.1376</v>
       </c>
       <c r="D117">
-        <v>107.05119999999999</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="2">
+        <v>107.0512</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="1">
         <v>46031</v>
       </c>
       <c r="B118" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C118">
         <v>101.6123</v>
@@ -2074,26 +2022,26 @@
         <v>106.5192</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="2">
+    <row r="119" spans="1:4">
+      <c r="A119" s="1">
         <v>46034</v>
       </c>
       <c r="B119" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C119">
         <v>100.8098</v>
       </c>
       <c r="D119">
-        <v>106.82769999999999</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="2">
+        <v>106.8277</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="1">
         <v>46035</v>
       </c>
       <c r="B120" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C120">
         <v>100.2574</v>
@@ -2102,26 +2050,26 @@
         <v>107.8578</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="2">
+    <row r="121" spans="1:4">
+      <c r="A121" s="1">
         <v>46036</v>
       </c>
       <c r="B121" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C121">
         <v>100.4748</v>
       </c>
       <c r="D121">
-        <v>108.42619999999999</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="2">
+        <v>108.4262</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="1">
         <v>46037</v>
       </c>
       <c r="B122" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C122">
         <v>101.6778</v>
@@ -2130,26 +2078,26 @@
         <v>106.4821</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="2">
+    <row r="123" spans="1:4">
+      <c r="A123" s="1">
         <v>46038</v>
       </c>
       <c r="B123" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C123">
         <v>100.8417</v>
       </c>
       <c r="D123">
-        <v>106.78400000000001</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="2">
+        <v>106.784</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="1">
         <v>46041</v>
       </c>
       <c r="B124" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C124">
         <v>101.07</v>
@@ -2158,26 +2106,26 @@
         <v>106.8882</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="2">
+    <row r="125" spans="1:4">
+      <c r="A125" s="1">
         <v>46042</v>
       </c>
       <c r="B125" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C125">
         <v>102.4316</v>
       </c>
       <c r="D125">
-        <v>107.28489999999999</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="2">
+        <v>107.2849</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="1">
         <v>46043</v>
       </c>
       <c r="B126" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C126">
         <v>101.2758</v>
@@ -2186,12 +2134,12 @@
         <v>108.715</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="2">
+    <row r="127" spans="1:4">
+      <c r="A127" s="1">
         <v>46044</v>
       </c>
       <c r="B127" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C127">
         <v>100.4006</v>
@@ -2200,40 +2148,40 @@
         <v>106.964</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="2">
+    <row r="128" spans="1:4">
+      <c r="A128" s="1">
         <v>46045</v>
       </c>
       <c r="B128" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C128">
-        <v>100.14660000000001</v>
+        <v>100.1466</v>
       </c>
       <c r="D128">
         <v>106.501</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="2">
+    <row r="129" spans="1:4">
+      <c r="A129" s="1">
         <v>46048</v>
       </c>
       <c r="B129" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C129">
-        <v>99.823999999999998</v>
+        <v>99.824</v>
       </c>
       <c r="D129">
         <v>107.0471</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="2">
+    <row r="130" spans="1:4">
+      <c r="A130" s="1">
         <v>46049</v>
       </c>
       <c r="B130" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C130">
         <v>100.4511</v>
@@ -2242,12 +2190,12 @@
         <v>105.7354</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" s="2">
+    <row r="131" spans="1:4">
+      <c r="A131" s="1">
         <v>46050</v>
       </c>
       <c r="B131" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C131">
         <v>100.6733</v>
@@ -2256,26 +2204,26 @@
         <v>107.0262</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="2">
+    <row r="132" spans="1:4">
+      <c r="A132" s="1">
         <v>46051</v>
       </c>
       <c r="B132" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C132">
-        <v>99.448899999999995</v>
+        <v>99.44889999999999</v>
       </c>
       <c r="D132">
         <v>107.3844</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="2">
+    <row r="133" spans="1:4">
+      <c r="A133" s="1">
         <v>46052</v>
       </c>
       <c r="B133" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C133">
         <v>99.863</v>
@@ -2284,26 +2232,26 @@
         <v>108.1546</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="2">
+    <row r="134" spans="1:4">
+      <c r="A134" s="1">
         <v>46055</v>
       </c>
       <c r="B134" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C134">
-        <v>99.500799999999998</v>
+        <v>99.5008</v>
       </c>
       <c r="D134">
         <v>107.7039</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="2">
+    <row r="135" spans="1:4">
+      <c r="A135" s="1">
         <v>46056</v>
       </c>
       <c r="B135" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C135">
         <v>100.4534</v>
@@ -2312,40 +2260,40 @@
         <v>108.4482</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="2">
+    <row r="136" spans="1:4">
+      <c r="A136" s="1">
         <v>46057</v>
       </c>
       <c r="B136" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C136">
         <v>100.0532</v>
       </c>
       <c r="D136">
-        <v>109.41849999999999</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="2">
+        <v>109.4185</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="1">
         <v>46058</v>
       </c>
       <c r="B137" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C137">
-        <v>99.648200000000003</v>
+        <v>99.6482</v>
       </c>
       <c r="D137">
         <v>109.6661</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="2">
+    <row r="138" spans="1:4">
+      <c r="A138" s="1">
         <v>46059</v>
       </c>
       <c r="B138" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C138">
         <v>100.0813</v>
@@ -2354,12 +2302,12 @@
         <v>109.9157</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="2">
+    <row r="139" spans="1:4">
+      <c r="A139" s="1">
         <v>46062</v>
       </c>
       <c r="B139" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C139">
         <v>100.6746</v>
@@ -2368,12 +2316,12 @@
         <v>110.1973</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="2">
+    <row r="140" spans="1:4">
+      <c r="A140" s="1">
         <v>46063</v>
       </c>
       <c r="B140" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C140">
         <v>101.0454</v>
@@ -2382,26 +2330,26 @@
         <v>109.4803</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="2">
+    <row r="141" spans="1:4">
+      <c r="A141" s="1">
         <v>46064</v>
       </c>
       <c r="B141" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C141">
-        <v>99.880799999999994</v>
+        <v>99.88079999999999</v>
       </c>
       <c r="D141">
-        <v>109.39490000000001</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" s="2">
+        <v>109.3949</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="1">
         <v>46065</v>
       </c>
       <c r="B142" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C142">
         <v>100.3128</v>
@@ -2410,68 +2358,68 @@
         <v>109.3052</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" s="2">
+    <row r="143" spans="1:4">
+      <c r="A143" s="1">
         <v>46066</v>
       </c>
       <c r="B143" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C143">
-        <v>99.622399999999999</v>
+        <v>99.6224</v>
       </c>
       <c r="D143">
         <v>109.6841</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="2">
+    <row r="144" spans="1:4">
+      <c r="A144" s="1">
         <v>46069</v>
       </c>
       <c r="B144" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C144">
-        <v>99.838200000000001</v>
+        <v>99.8382</v>
       </c>
       <c r="D144">
         <v>110.6053</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" s="2">
+    <row r="145" spans="1:4">
+      <c r="A145" s="1">
         <v>46070</v>
       </c>
       <c r="B145" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C145">
-        <v>98.873900000000006</v>
+        <v>98.87390000000001</v>
       </c>
       <c r="D145">
         <v>109.7129</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="2">
+    <row r="146" spans="1:4">
+      <c r="A146" s="1">
         <v>46071</v>
       </c>
       <c r="B146" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C146">
-        <v>99.236900000000006</v>
+        <v>99.23690000000001</v>
       </c>
       <c r="D146">
-        <v>109.64709999999999</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="2">
+        <v>109.6471</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="1">
         <v>46072</v>
       </c>
       <c r="B147" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C147">
         <v>98.7149</v>
@@ -2480,236 +2428,236 @@
         <v>110.9905</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" s="2">
+    <row r="148" spans="1:4">
+      <c r="A148" s="1">
         <v>46073</v>
       </c>
       <c r="B148" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C148">
-        <v>97.860799999999998</v>
+        <v>97.8608</v>
       </c>
       <c r="D148">
         <v>110.3746</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="2">
+    <row r="149" spans="1:4">
+      <c r="A149" s="1">
         <v>46076</v>
       </c>
       <c r="B149" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C149">
-        <v>98.406599999999997</v>
+        <v>98.4066</v>
       </c>
       <c r="D149">
         <v>109.6927</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="2">
+    <row r="150" spans="1:4">
+      <c r="A150" s="1">
         <v>46077</v>
       </c>
       <c r="B150" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C150">
-        <v>98.624300000000005</v>
+        <v>98.62430000000001</v>
       </c>
       <c r="D150">
         <v>109.9141</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="2">
+    <row r="151" spans="1:4">
+      <c r="A151" s="1">
         <v>46078</v>
       </c>
       <c r="B151" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C151">
-        <v>98.240899999999996</v>
+        <v>98.2409</v>
       </c>
       <c r="D151">
-        <v>110.70059999999999</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A152" s="2">
+        <v>110.7006</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="1">
         <v>46079</v>
       </c>
       <c r="B152" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C152">
-        <v>99.305300000000003</v>
+        <v>99.3053</v>
       </c>
       <c r="D152">
         <v>110.755</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A153" s="2">
+    <row r="153" spans="1:4">
+      <c r="A153" s="1">
         <v>46080</v>
       </c>
       <c r="B153" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C153">
-        <v>99.042000000000002</v>
+        <v>99.042</v>
       </c>
       <c r="D153">
         <v>111.9768</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A154" s="2">
+    <row r="154" spans="1:4">
+      <c r="A154" s="1">
         <v>46083</v>
       </c>
       <c r="B154" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C154">
-        <v>99.113100000000003</v>
+        <v>99.1131</v>
       </c>
       <c r="D154">
         <v>112.7891</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" s="2">
+    <row r="155" spans="1:4">
+      <c r="A155" s="1">
         <v>46084</v>
       </c>
       <c r="B155" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C155">
-        <v>99.351600000000005</v>
+        <v>99.3516</v>
       </c>
       <c r="D155">
         <v>113.5938</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A156" s="2">
+    <row r="156" spans="1:4">
+      <c r="A156" s="1">
         <v>46085</v>
       </c>
       <c r="B156" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C156">
-        <v>98.961500000000001</v>
+        <v>98.9615</v>
       </c>
       <c r="D156">
-        <v>114.14279999999999</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A157" s="2">
+        <v>114.1428</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="1">
         <v>46086</v>
       </c>
       <c r="B157" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C157">
-        <v>99.342200000000005</v>
+        <v>99.34220000000001</v>
       </c>
       <c r="D157">
         <v>116.3139</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A158" s="2">
+    <row r="158" spans="1:4">
+      <c r="A158" s="1">
         <v>46087</v>
       </c>
       <c r="B158" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C158">
-        <v>99.013099999999994</v>
+        <v>99.01309999999999</v>
       </c>
       <c r="D158">
         <v>116.1695</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A159" s="2">
+    <row r="159" spans="1:4">
+      <c r="A159" s="1">
         <v>46090</v>
       </c>
       <c r="B159" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C159">
-        <v>98.771100000000004</v>
+        <v>98.7711</v>
       </c>
       <c r="D159">
         <v>114.354</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A160" s="2">
+    <row r="160" spans="1:4">
+      <c r="A160" s="1">
         <v>46091</v>
       </c>
       <c r="B160" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C160">
-        <v>99.778800000000004</v>
+        <v>99.7788</v>
       </c>
       <c r="D160">
         <v>115.8674</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A161" s="2">
+    <row r="161" spans="1:4">
+      <c r="A161" s="1">
         <v>46092</v>
       </c>
       <c r="B161" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C161">
-        <v>99.087599999999995</v>
+        <v>99.08759999999999</v>
       </c>
       <c r="D161">
-        <v>115.48950000000001</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A162" s="2">
+        <v>115.4895</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="1">
         <v>46093</v>
       </c>
       <c r="B162" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C162">
-        <v>97.432000000000002</v>
+        <v>97.432</v>
       </c>
       <c r="D162">
         <v>115.6354</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A163" s="2">
+    <row r="163" spans="1:4">
+      <c r="A163" s="1">
         <v>46094</v>
       </c>
       <c r="B163" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C163">
-        <v>98.598500000000001</v>
+        <v>98.5985</v>
       </c>
       <c r="D163">
         <v>116.893</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="2">
+    <row r="164" spans="1:4">
+      <c r="A164" s="1">
         <v>46097</v>
       </c>
       <c r="B164" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C164">
         <v>100.4384</v>
@@ -2718,54 +2666,54 @@
         <v>115.4415</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A165" s="2">
+    <row r="165" spans="1:4">
+      <c r="A165" s="1">
         <v>46098</v>
       </c>
       <c r="B165" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C165">
-        <v>100.19750000000001</v>
+        <v>100.1975</v>
       </c>
       <c r="D165">
         <v>114.3317</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A166" s="2">
+    <row r="166" spans="1:4">
+      <c r="A166" s="1">
         <v>46099</v>
       </c>
       <c r="B166" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C166">
-        <v>98.863200000000006</v>
+        <v>98.86320000000001</v>
       </c>
       <c r="D166">
         <v>112.9128</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A167" s="2">
+    <row r="167" spans="1:4">
+      <c r="A167" s="1">
         <v>46100</v>
       </c>
       <c r="B167" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C167">
-        <v>98.692899999999995</v>
+        <v>98.69289999999999</v>
       </c>
       <c r="D167">
         <v>112.2406</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A168" s="2">
+    <row r="168" spans="1:4">
+      <c r="A168" s="1">
         <v>46101</v>
       </c>
       <c r="B168" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C168">
         <v>98.5398</v>
@@ -2774,124 +2722,124 @@
         <v>112.6803</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A169" s="2">
+    <row r="169" spans="1:4">
+      <c r="A169" s="1">
         <v>46104</v>
       </c>
       <c r="B169" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C169">
-        <v>98.454700000000003</v>
+        <v>98.4547</v>
       </c>
       <c r="D169">
         <v>113.1979</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A170" s="2">
+    <row r="170" spans="1:4">
+      <c r="A170" s="1">
         <v>46105</v>
       </c>
       <c r="B170" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C170">
-        <v>97.721500000000006</v>
+        <v>97.72150000000001</v>
       </c>
       <c r="D170">
-        <v>113.49339999999999</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A171" s="2">
+        <v>113.4934</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="1">
         <v>46106</v>
       </c>
       <c r="B171" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C171">
-        <v>98.173100000000005</v>
+        <v>98.17310000000001</v>
       </c>
       <c r="D171">
         <v>112.256</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A172" s="2">
+    <row r="172" spans="1:4">
+      <c r="A172" s="1">
         <v>46107</v>
       </c>
       <c r="B172" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C172">
-        <v>98.588200000000001</v>
+        <v>98.5882</v>
       </c>
       <c r="D172">
         <v>110.2264</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" s="2">
+    <row r="173" spans="1:4">
+      <c r="A173" s="1">
         <v>46108</v>
       </c>
       <c r="B173" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C173">
-        <v>97.586299999999994</v>
+        <v>97.58629999999999</v>
       </c>
       <c r="D173">
         <v>110.3184</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A174" s="2">
+    <row r="174" spans="1:4">
+      <c r="A174" s="1">
         <v>46111</v>
       </c>
       <c r="B174" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C174">
-        <v>98.120400000000004</v>
+        <v>98.1204</v>
       </c>
       <c r="D174">
         <v>109.9461</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A175" s="2">
+    <row r="175" spans="1:4">
+      <c r="A175" s="1">
         <v>46112</v>
       </c>
       <c r="B175" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C175">
-        <v>99.604100000000003</v>
+        <v>99.6041</v>
       </c>
       <c r="D175">
         <v>110.3942</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" s="2">
+    <row r="176" spans="1:4">
+      <c r="A176" s="1">
         <v>46113</v>
       </c>
       <c r="B176" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C176">
-        <v>99.775000000000006</v>
+        <v>99.77500000000001</v>
       </c>
       <c r="D176">
         <v>111.0583</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A177" s="2">
+    <row r="177" spans="1:4">
+      <c r="A177" s="1">
         <v>46114</v>
       </c>
       <c r="B177" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C177">
         <v>99.5839</v>
@@ -2900,26 +2848,26 @@
         <v>111.2255</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A178" s="2">
+    <row r="178" spans="1:4">
+      <c r="A178" s="1">
         <v>46115</v>
       </c>
       <c r="B178" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C178">
-        <v>99.531899999999993</v>
+        <v>99.53189999999999</v>
       </c>
       <c r="D178">
         <v>111.9464</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A179" s="2">
+    <row r="179" spans="1:4">
+      <c r="A179" s="1">
         <v>46118</v>
       </c>
       <c r="B179" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C179">
         <v>100.0171</v>
@@ -2928,54 +2876,54 @@
         <v>112.1964</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A180" s="2">
+    <row r="180" spans="1:4">
+      <c r="A180" s="1">
         <v>46119</v>
       </c>
       <c r="B180" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C180">
-        <v>98.832300000000004</v>
+        <v>98.8323</v>
       </c>
       <c r="D180">
         <v>112.7171</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A181" s="2">
+    <row r="181" spans="1:4">
+      <c r="A181" s="1">
         <v>46120</v>
       </c>
       <c r="B181" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C181">
-        <v>98.996499999999997</v>
+        <v>98.9965</v>
       </c>
       <c r="D181">
         <v>112.1267</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A182" s="2">
+    <row r="182" spans="1:4">
+      <c r="A182" s="1">
         <v>46121</v>
       </c>
       <c r="B182" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C182">
-        <v>98.769400000000005</v>
+        <v>98.7694</v>
       </c>
       <c r="D182">
-        <v>112.01049999999999</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A183" s="2">
+        <v>112.0105</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" s="1">
         <v>46122</v>
       </c>
       <c r="B183" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C183">
         <v>100.1187</v>
@@ -2984,26 +2932,26 @@
         <v>112.2316</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A184" s="2">
+    <row r="184" spans="1:4">
+      <c r="A184" s="1">
         <v>46125</v>
       </c>
       <c r="B184" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C184">
-        <v>100.04340000000001</v>
+        <v>100.0434</v>
       </c>
       <c r="D184">
         <v>113.0132</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A185" s="2">
+    <row r="185" spans="1:4">
+      <c r="A185" s="1">
         <v>46126</v>
       </c>
       <c r="B185" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C185">
         <v>101.2818</v>
@@ -3012,12 +2960,12 @@
         <v>112.7024</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A186" s="2">
+    <row r="186" spans="1:4">
+      <c r="A186" s="1">
         <v>46127</v>
       </c>
       <c r="B186" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C186">
         <v>100.5346</v>
@@ -3026,12 +2974,12 @@
         <v>113.2174</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A187" s="2">
+    <row r="187" spans="1:4">
+      <c r="A187" s="1">
         <v>46128</v>
       </c>
       <c r="B187" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C187">
         <v>101.0046</v>
@@ -3040,26 +2988,26 @@
         <v>113.0219</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A188" s="2">
+    <row r="188" spans="1:4">
+      <c r="A188" s="1">
         <v>46129</v>
       </c>
       <c r="B188" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C188">
-        <v>101.28400000000001</v>
+        <v>101.284</v>
       </c>
       <c r="D188">
-        <v>112.96080000000001</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A189" s="2">
+        <v>112.9608</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" s="1">
         <v>46132</v>
       </c>
       <c r="B189" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C189">
         <v>100.7062</v>
@@ -3068,68 +3016,68 @@
         <v>113.7557</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A190" s="2">
+    <row r="190" spans="1:4">
+      <c r="A190" s="1">
         <v>46133</v>
       </c>
       <c r="B190" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C190">
-        <v>100.88290000000001</v>
+        <v>100.8829</v>
       </c>
       <c r="D190">
-        <v>111.98739999999999</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A191" s="2">
+        <v>111.9874</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" s="1">
         <v>46134</v>
       </c>
       <c r="B191" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C191">
-        <v>101.80419999999999</v>
+        <v>101.8042</v>
       </c>
       <c r="D191">
         <v>110.8707</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A192" s="2">
+    <row r="192" spans="1:4">
+      <c r="A192" s="1">
         <v>46135</v>
       </c>
       <c r="B192" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C192">
         <v>101.6191</v>
       </c>
       <c r="D192">
-        <v>109.60039999999999</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A193" s="2">
+        <v>109.6004</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" s="1">
         <v>46136</v>
       </c>
       <c r="B193" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C193">
-        <v>100.44329999999999</v>
+        <v>100.4433</v>
       </c>
       <c r="D193">
         <v>107.5981</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A194" s="2">
+    <row r="194" spans="1:4">
+      <c r="A194" s="1">
         <v>46139</v>
       </c>
       <c r="B194" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C194">
         <v>100.4799</v>
@@ -3138,110 +3086,110 @@
         <v>107.0573</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A195" s="2">
+    <row r="195" spans="1:4">
+      <c r="A195" s="1">
         <v>46140</v>
       </c>
       <c r="B195" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C195">
-        <v>99.882800000000003</v>
+        <v>99.8828</v>
       </c>
       <c r="D195">
         <v>107.742</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A196" s="2">
+    <row r="196" spans="1:4">
+      <c r="A196" s="1">
         <v>46141</v>
       </c>
       <c r="B196" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C196">
-        <v>99.687899999999999</v>
+        <v>99.6879</v>
       </c>
       <c r="D196">
         <v>107.5395</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A197" s="2">
+    <row r="197" spans="1:4">
+      <c r="A197" s="1">
         <v>46142</v>
       </c>
       <c r="B197" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C197">
-        <v>99.678799999999995</v>
+        <v>99.6788</v>
       </c>
       <c r="D197">
         <v>107.7527</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A198" s="2">
+    <row r="198" spans="1:4">
+      <c r="A198" s="1">
         <v>46143</v>
       </c>
       <c r="B198" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C198">
-        <v>98.515699999999995</v>
+        <v>98.5157</v>
       </c>
       <c r="D198">
         <v>108.7347</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A199" s="2">
+    <row r="199" spans="1:4">
+      <c r="A199" s="1">
         <v>46146</v>
       </c>
       <c r="B199" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C199">
-        <v>97.429400000000001</v>
+        <v>97.4294</v>
       </c>
       <c r="D199">
         <v>109.9331</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A200" s="2">
+    <row r="200" spans="1:4">
+      <c r="A200" s="1">
         <v>46147</v>
       </c>
       <c r="B200" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C200">
-        <v>97.811899999999994</v>
+        <v>97.81189999999999</v>
       </c>
       <c r="D200">
-        <v>109.91630000000001</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A201" s="2">
+        <v>109.9163</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="1">
         <v>46148</v>
       </c>
       <c r="B201" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C201">
         <v>97.4953</v>
       </c>
       <c r="D201">
-        <v>111.15049999999999</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A202" s="2">
+        <v>111.1505</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="1">
         <v>46149</v>
       </c>
       <c r="B202" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C202">
         <v>95.7607</v>
@@ -3250,152 +3198,152 @@
         <v>111.2769</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A203" s="2">
+    <row r="203" spans="1:4">
+      <c r="A203" s="1">
         <v>46150</v>
       </c>
       <c r="B203" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C203">
-        <v>96.343299999999999</v>
+        <v>96.3433</v>
       </c>
       <c r="D203">
-        <v>110.57599999999999</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A204" s="2">
+        <v>110.576</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="1">
         <v>46153</v>
       </c>
       <c r="B204" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C204">
-        <v>96.577600000000004</v>
+        <v>96.5776</v>
       </c>
       <c r="D204">
-        <v>110.09439999999999</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A205" s="2">
+        <v>110.0944</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="1">
         <v>46154</v>
       </c>
       <c r="B205" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C205">
-        <v>96.133399999999995</v>
+        <v>96.13339999999999</v>
       </c>
       <c r="D205">
         <v>108.8344</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A206" s="2">
+    <row r="206" spans="1:4">
+      <c r="A206" s="1">
         <v>46155</v>
       </c>
       <c r="B206" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C206">
-        <v>95.278099999999995</v>
+        <v>95.27809999999999</v>
       </c>
       <c r="D206">
-        <v>108.10469999999999</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A207" s="2">
+        <v>108.1047</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="1">
         <v>46156</v>
       </c>
       <c r="B207" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C207">
-        <v>95.892399999999995</v>
+        <v>95.89239999999999</v>
       </c>
       <c r="D207">
         <v>107.8383</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A208" s="2">
+    <row r="208" spans="1:4">
+      <c r="A208" s="1">
         <v>46157</v>
       </c>
       <c r="B208" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C208">
-        <v>96.178200000000004</v>
+        <v>96.1782</v>
       </c>
       <c r="D208">
-        <v>108.57470000000001</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A209" s="2">
+        <v>108.5747</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="1">
         <v>46160</v>
       </c>
       <c r="B209" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C209">
-        <v>97.858699999999999</v>
+        <v>97.8587</v>
       </c>
       <c r="D209">
-        <v>110.11279999999999</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A210" s="2">
+        <v>110.1128</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="1">
         <v>46161</v>
       </c>
       <c r="B210" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C210">
-        <v>98.199700000000007</v>
+        <v>98.19970000000001</v>
       </c>
       <c r="D210">
         <v>108.9393</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A211" s="2">
+    <row r="211" spans="1:4">
+      <c r="A211" s="1">
         <v>46162</v>
       </c>
       <c r="B211" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C211">
-        <v>98.519099999999995</v>
+        <v>98.51909999999999</v>
       </c>
       <c r="D211">
         <v>109.3252</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A212" s="2">
+    <row r="212" spans="1:4">
+      <c r="A212" s="1">
         <v>46163</v>
       </c>
       <c r="B212" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C212">
-        <v>98.450199999999995</v>
+        <v>98.4502</v>
       </c>
       <c r="D212">
         <v>108.4589</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A213" s="2">
+    <row r="213" spans="1:4">
+      <c r="A213" s="1">
         <v>46164</v>
       </c>
       <c r="B213" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C213">
         <v>99.0715</v>
@@ -3404,96 +3352,96 @@
         <v>108.9141</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A214" s="2">
+    <row r="214" spans="1:4">
+      <c r="A214" s="1">
         <v>46167</v>
       </c>
       <c r="B214" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C214">
-        <v>99.561499999999995</v>
+        <v>99.5615</v>
       </c>
       <c r="D214">
-        <v>108.84350000000001</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A215" s="2">
+        <v>108.8435</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="1">
         <v>46168</v>
       </c>
       <c r="B215" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C215">
-        <v>100.49850000000001</v>
+        <v>100.4985</v>
       </c>
       <c r="D215">
         <v>107.2927</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A216" s="2">
+    <row r="216" spans="1:4">
+      <c r="A216" s="1">
         <v>46169</v>
       </c>
       <c r="B216" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C216">
         <v>100.1743</v>
       </c>
       <c r="D216">
-        <v>108.13249999999999</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A217" s="2">
+        <v>108.1325</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="1">
         <v>46170</v>
       </c>
       <c r="B217" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C217">
-        <v>99.912400000000005</v>
+        <v>99.91240000000001</v>
       </c>
       <c r="D217">
         <v>107.6524</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A218" s="2">
+    <row r="218" spans="1:4">
+      <c r="A218" s="1">
         <v>46171</v>
       </c>
       <c r="B218" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C218">
-        <v>99.620199999999997</v>
+        <v>99.6202</v>
       </c>
       <c r="D218">
-        <v>107.23560000000001</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A219" s="2">
+        <v>107.2356</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="1">
         <v>46174</v>
       </c>
       <c r="B219" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C219">
-        <v>100.23050000000001</v>
+        <v>100.2305</v>
       </c>
       <c r="D219">
         <v>106.3608</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A220" s="2">
+    <row r="220" spans="1:4">
+      <c r="A220" s="1">
         <v>46175</v>
       </c>
       <c r="B220" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C220">
         <v>101.3501</v>
@@ -3502,12 +3450,12 @@
         <v>105.8466</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A221" s="2">
+    <row r="221" spans="1:4">
+      <c r="A221" s="1">
         <v>46176</v>
       </c>
       <c r="B221" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C221">
         <v>101.0682</v>
@@ -3516,40 +3464,40 @@
         <v>106.2513</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A222" s="2">
+    <row r="222" spans="1:4">
+      <c r="A222" s="1">
         <v>46177</v>
       </c>
       <c r="B222" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C222">
         <v>100.8117</v>
       </c>
       <c r="D222">
-        <v>106.13290000000001</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A223" s="2">
+        <v>106.1329</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="1">
         <v>46178</v>
       </c>
       <c r="B223" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C223">
-        <v>101.08669999999999</v>
+        <v>101.0867</v>
       </c>
       <c r="D223">
-        <v>106.45440000000001</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A224" s="2">
+        <v>106.4544</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="1">
         <v>46181</v>
       </c>
       <c r="B224" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C224">
         <v>100.9592</v>
@@ -3558,26 +3506,26 @@
         <v>106.8052</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A225" s="2">
+    <row r="225" spans="1:4">
+      <c r="A225" s="1">
         <v>46182</v>
       </c>
       <c r="B225" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C225">
-        <v>101.69370000000001</v>
+        <v>101.6937</v>
       </c>
       <c r="D225">
         <v>107.9764</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A226" s="2">
+    <row r="226" spans="1:4">
+      <c r="A226" s="1">
         <v>46183</v>
       </c>
       <c r="B226" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C226">
         <v>100.1113</v>
@@ -3586,40 +3534,40 @@
         <v>107.7235</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A227" s="2">
+    <row r="227" spans="1:4">
+      <c r="A227" s="1">
         <v>46184</v>
       </c>
       <c r="B227" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C227">
-        <v>99.570400000000006</v>
+        <v>99.57040000000001</v>
       </c>
       <c r="D227">
-        <v>106.49379999999999</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A228" s="2">
+        <v>106.4938</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="1">
         <v>46185</v>
       </c>
       <c r="B228" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C228">
-        <v>99.063800000000001</v>
+        <v>99.0638</v>
       </c>
       <c r="D228">
         <v>107.4456</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A229" s="2">
+    <row r="229" spans="1:4">
+      <c r="A229" s="1">
         <v>46188</v>
       </c>
       <c r="B229" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C229">
         <v>97.4739</v>
@@ -3628,152 +3576,152 @@
         <v>107.2037</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A230" s="2">
+    <row r="230" spans="1:4">
+      <c r="A230" s="1">
         <v>46189</v>
       </c>
       <c r="B230" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C230">
-        <v>96.852099999999993</v>
+        <v>96.85209999999999</v>
       </c>
       <c r="D230">
         <v>108.2025</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A231" s="2">
+    <row r="231" spans="1:4">
+      <c r="A231" s="1">
         <v>46190</v>
       </c>
       <c r="B231" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C231">
-        <v>96.267700000000005</v>
+        <v>96.2677</v>
       </c>
       <c r="D231">
         <v>108.5776</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A232" s="2">
+    <row r="232" spans="1:4">
+      <c r="A232" s="1">
         <v>46191</v>
       </c>
       <c r="B232" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C232">
         <v>96.1768</v>
       </c>
       <c r="D232">
-        <v>108.50709999999999</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A233" s="2">
+        <v>108.5071</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="1">
         <v>46192</v>
       </c>
       <c r="B233" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C233">
-        <v>96.986900000000006</v>
+        <v>96.98690000000001</v>
       </c>
       <c r="D233">
         <v>108.8533</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A234" s="2">
+    <row r="234" spans="1:4">
+      <c r="A234" s="1">
         <v>46195</v>
       </c>
       <c r="B234" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C234">
-        <v>96.864999999999995</v>
+        <v>96.86499999999999</v>
       </c>
       <c r="D234">
         <v>110.5958</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A235" s="2">
+    <row r="235" spans="1:4">
+      <c r="A235" s="1">
         <v>46196</v>
       </c>
       <c r="B235" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C235">
-        <v>96.200699999999998</v>
+        <v>96.2007</v>
       </c>
       <c r="D235">
         <v>112.4777</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A236" s="2">
+    <row r="236" spans="1:4">
+      <c r="A236" s="1">
         <v>46197</v>
       </c>
       <c r="B236" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C236">
-        <v>96.208699999999993</v>
+        <v>96.20869999999999</v>
       </c>
       <c r="D236">
         <v>112.5851</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A237" s="2">
+    <row r="237" spans="1:4">
+      <c r="A237" s="1">
         <v>46198</v>
       </c>
       <c r="B237" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C237">
-        <v>96.975399999999993</v>
+        <v>96.97539999999999</v>
       </c>
       <c r="D237">
         <v>112.7744</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A238" s="2">
+    <row r="238" spans="1:4">
+      <c r="A238" s="1">
         <v>46199</v>
       </c>
       <c r="B238" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C238">
-        <v>96.348200000000006</v>
+        <v>96.34820000000001</v>
       </c>
       <c r="D238">
-        <v>113.79049999999999</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A239" s="2">
+        <v>113.7905</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="1">
         <v>46202</v>
       </c>
       <c r="B239" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C239">
         <v>95.77</v>
       </c>
       <c r="D239">
-        <v>113.06619999999999</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A240" s="2">
+        <v>113.0662</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="1">
         <v>46203</v>
       </c>
       <c r="B240" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C240">
         <v>96.1982</v>
@@ -3782,124 +3730,124 @@
         <v>113.4127</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A241" s="2">
+    <row r="241" spans="1:4">
+      <c r="A241" s="1">
         <v>46204</v>
       </c>
       <c r="B241" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C241">
-        <v>96.093400000000003</v>
+        <v>96.0934</v>
       </c>
       <c r="D241">
         <v>113.4346</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A242" s="2">
+    <row r="242" spans="1:4">
+      <c r="A242" s="1">
         <v>46205</v>
       </c>
       <c r="B242" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C242">
-        <v>96.584000000000003</v>
+        <v>96.584</v>
       </c>
       <c r="D242">
         <v>113.7649</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A243" s="2">
+    <row r="243" spans="1:4">
+      <c r="A243" s="1">
         <v>46206</v>
       </c>
       <c r="B243" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C243">
-        <v>96.621899999999997</v>
+        <v>96.6219</v>
       </c>
       <c r="D243">
         <v>113.0519</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A244" s="2">
+    <row r="244" spans="1:4">
+      <c r="A244" s="1">
         <v>46209</v>
       </c>
       <c r="B244" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C244">
         <v>97.1524</v>
       </c>
       <c r="D244">
-        <v>111.65949999999999</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A245" s="2">
+        <v>111.6595</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="1">
         <v>46210</v>
       </c>
       <c r="B245" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C245">
-        <v>96.483199999999997</v>
+        <v>96.4832</v>
       </c>
       <c r="D245">
         <v>109.8524</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A246" s="2">
+    <row r="246" spans="1:4">
+      <c r="A246" s="1">
         <v>46211</v>
       </c>
       <c r="B246" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C246">
-        <v>96.522099999999995</v>
+        <v>96.52209999999999</v>
       </c>
       <c r="D246">
         <v>108.9144</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A247" s="2">
+    <row r="247" spans="1:4">
+      <c r="A247" s="1">
         <v>46212</v>
       </c>
       <c r="B247" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C247">
-        <v>96.424400000000006</v>
+        <v>96.42440000000001</v>
       </c>
       <c r="D247">
         <v>108.5583</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A248" s="2">
+    <row r="248" spans="1:4">
+      <c r="A248" s="1">
         <v>46213</v>
       </c>
       <c r="B248" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C248">
-        <v>95.635999999999996</v>
+        <v>95.636</v>
       </c>
       <c r="D248">
         <v>108.3471</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A249" s="2">
+    <row r="249" spans="1:4">
+      <c r="A249" s="1">
         <v>45869</v>
       </c>
       <c r="B249" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -3908,12 +3856,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A250" s="2">
+    <row r="250" spans="1:4">
+      <c r="A250" s="1">
         <v>45870</v>
       </c>
       <c r="B250" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -3922,12 +3870,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A251" s="2">
+    <row r="251" spans="1:4">
+      <c r="A251" s="1">
         <v>45873</v>
       </c>
       <c r="B251" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -3936,12 +3884,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A252" s="2">
+    <row r="252" spans="1:4">
+      <c r="A252" s="1">
         <v>45874</v>
       </c>
       <c r="B252" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -3950,12 +3898,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A253" s="2">
+    <row r="253" spans="1:4">
+      <c r="A253" s="1">
         <v>45875</v>
       </c>
       <c r="B253" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -3964,110 +3912,110 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A254" s="2">
+    <row r="254" spans="1:4">
+      <c r="A254" s="1">
         <v>45876</v>
       </c>
       <c r="B254" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C254">
-        <v>96.917199999999994</v>
+        <v>96.91719999999999</v>
       </c>
       <c r="D254">
-        <v>99.779600000000002</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A255" s="2">
+        <v>99.7796</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="1">
         <v>45877</v>
       </c>
       <c r="B255" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C255">
-        <v>96.229600000000005</v>
+        <v>96.2296</v>
       </c>
       <c r="D255">
-        <v>101.82899999999999</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A256" s="2">
+        <v>101.829</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="1">
         <v>45880</v>
       </c>
       <c r="B256" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C256">
-        <v>97.418199999999999</v>
+        <v>97.4182</v>
       </c>
       <c r="D256">
-        <v>103.39870000000001</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A257" s="2">
+        <v>103.3987</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="1">
         <v>45881</v>
       </c>
       <c r="B257" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C257">
-        <v>97.684899999999999</v>
+        <v>97.6849</v>
       </c>
       <c r="D257">
         <v>102.7343</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A258" s="2">
+    <row r="258" spans="1:4">
+      <c r="A258" s="1">
         <v>45882</v>
       </c>
       <c r="B258" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C258">
         <v>98.3386</v>
       </c>
       <c r="D258">
-        <v>102.53919999999999</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A259" s="2">
+        <v>102.5392</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="1">
         <v>45883</v>
       </c>
       <c r="B259" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C259">
-        <v>97.466700000000003</v>
+        <v>97.4667</v>
       </c>
       <c r="D259">
         <v>101.3797</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A260" s="2">
+    <row r="260" spans="1:4">
+      <c r="A260" s="1">
         <v>45884</v>
       </c>
       <c r="B260" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C260">
-        <v>96.618899999999996</v>
+        <v>96.6189</v>
       </c>
       <c r="D260">
-        <v>100.94119999999999</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A261" s="2">
+        <v>100.9412</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="1">
         <v>45887</v>
       </c>
       <c r="B261" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C261">
         <v>97.0137</v>
@@ -4076,614 +4024,614 @@
         <v>101.2364</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A262" s="2">
+    <row r="262" spans="1:4">
+      <c r="A262" s="1">
         <v>45888</v>
       </c>
       <c r="B262" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C262">
-        <v>97.101799999999997</v>
+        <v>97.1018</v>
       </c>
       <c r="D262">
         <v>102.2535</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A263" s="2">
+    <row r="263" spans="1:4">
+      <c r="A263" s="1">
         <v>45889</v>
       </c>
       <c r="B263" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C263">
-        <v>97.578500000000005</v>
+        <v>97.57850000000001</v>
       </c>
       <c r="D263">
-        <v>101.69799999999999</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A264" s="2">
+        <v>101.698</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="1">
         <v>45890</v>
       </c>
       <c r="B264" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C264">
-        <v>97.471400000000003</v>
+        <v>97.4714</v>
       </c>
       <c r="D264">
-        <v>101.20650000000001</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A265" s="2">
+        <v>101.2065</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="1">
         <v>45891</v>
       </c>
       <c r="B265" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C265">
-        <v>97.734800000000007</v>
+        <v>97.73480000000001</v>
       </c>
       <c r="D265">
-        <v>99.508399999999995</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A266" s="2">
+        <v>99.50839999999999</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="1">
         <v>45894</v>
       </c>
       <c r="B266" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C266">
-        <v>97.903199999999998</v>
+        <v>97.9032</v>
       </c>
       <c r="D266">
-        <v>99.418700000000001</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A267" s="2">
+        <v>99.4187</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="1">
         <v>45895</v>
       </c>
       <c r="B267" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C267">
-        <v>98.566699999999997</v>
+        <v>98.5667</v>
       </c>
       <c r="D267">
-        <v>98.613500000000002</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A268" s="2">
+        <v>98.6135</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="1">
         <v>45896</v>
       </c>
       <c r="B268" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C268">
-        <v>99.258200000000002</v>
+        <v>99.2582</v>
       </c>
       <c r="D268">
-        <v>98.235299999999995</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A269" s="2">
+        <v>98.2353</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="1">
         <v>45897</v>
       </c>
       <c r="B269" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C269">
-        <v>97.989699999999999</v>
+        <v>97.9897</v>
       </c>
       <c r="D269">
-        <v>97.585400000000007</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A270" s="2">
+        <v>97.58540000000001</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="1">
         <v>45898</v>
       </c>
       <c r="B270" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C270">
-        <v>96.236000000000004</v>
+        <v>96.236</v>
       </c>
       <c r="D270">
-        <v>97.550899999999999</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A271" s="2">
+        <v>97.5509</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="1">
         <v>45901</v>
       </c>
       <c r="B271" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C271">
-        <v>97.063999999999993</v>
+        <v>97.06399999999999</v>
       </c>
       <c r="D271">
-        <v>96.218199999999996</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A272" s="2">
+        <v>96.2182</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="1">
         <v>45902</v>
       </c>
       <c r="B272" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C272">
-        <v>98.046400000000006</v>
+        <v>98.04640000000001</v>
       </c>
       <c r="D272">
-        <v>95.127399999999994</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A273" s="2">
+        <v>95.12739999999999</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="1">
         <v>45903</v>
       </c>
       <c r="B273" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C273">
         <v>97.2727</v>
       </c>
       <c r="D273">
-        <v>96.785899999999998</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A274" s="2">
+        <v>96.7859</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="1">
         <v>45904</v>
       </c>
       <c r="B274" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C274">
-        <v>95.839200000000005</v>
+        <v>95.83920000000001</v>
       </c>
       <c r="D274">
-        <v>95.827699999999993</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A275" s="2">
+        <v>95.82769999999999</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="1">
         <v>45905</v>
       </c>
       <c r="B275" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C275">
-        <v>95.958100000000002</v>
+        <v>95.9581</v>
       </c>
       <c r="D275">
-        <v>95.025199999999998</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A276" s="2">
+        <v>95.0252</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="1">
         <v>45908</v>
       </c>
       <c r="B276" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C276">
-        <v>96.728300000000004</v>
+        <v>96.7283</v>
       </c>
       <c r="D276">
-        <v>96.459699999999998</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A277" s="2">
+        <v>96.4597</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="1">
         <v>45909</v>
       </c>
       <c r="B277" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C277">
-        <v>98.188400000000001</v>
+        <v>98.1884</v>
       </c>
       <c r="D277">
-        <v>98.74</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A278" s="2">
+        <v>98.73999999999999</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="1">
         <v>45910</v>
       </c>
       <c r="B278" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C278">
-        <v>98.644499999999994</v>
+        <v>98.64449999999999</v>
       </c>
       <c r="D278">
-        <v>97.854100000000003</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A279" s="2">
+        <v>97.8541</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="1">
         <v>45911</v>
       </c>
       <c r="B279" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C279">
-        <v>98.388099999999994</v>
+        <v>98.38809999999999</v>
       </c>
       <c r="D279">
-        <v>97.605000000000004</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A280" s="2">
+        <v>97.605</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="1">
         <v>45912</v>
       </c>
       <c r="B280" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C280">
-        <v>97.713999999999999</v>
+        <v>97.714</v>
       </c>
       <c r="D280">
-        <v>97.910700000000006</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A281" s="2">
+        <v>97.91070000000001</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="1">
         <v>45915</v>
       </c>
       <c r="B281" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C281">
-        <v>97.765500000000003</v>
+        <v>97.7655</v>
       </c>
       <c r="D281">
-        <v>99.303899999999999</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A282" s="2">
+        <v>99.3039</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="1">
         <v>45916</v>
       </c>
       <c r="B282" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C282">
-        <v>97.569199999999995</v>
+        <v>97.5692</v>
       </c>
       <c r="D282">
-        <v>98.559700000000007</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A283" s="2">
+        <v>98.55970000000001</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="1">
         <v>45917</v>
       </c>
       <c r="B283" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C283">
-        <v>96.803600000000003</v>
+        <v>96.8036</v>
       </c>
       <c r="D283">
-        <v>98.405699999999996</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A284" s="2">
+        <v>98.4057</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="1">
         <v>45918</v>
       </c>
       <c r="B284" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C284">
-        <v>98.463200000000001</v>
+        <v>98.4632</v>
       </c>
       <c r="D284">
-        <v>99.057000000000002</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A285" s="2">
+        <v>99.057</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="1">
         <v>45919</v>
       </c>
       <c r="B285" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C285">
-        <v>99.939599999999999</v>
+        <v>99.9396</v>
       </c>
       <c r="D285">
-        <v>99.441199999999995</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A286" s="2">
+        <v>99.44119999999999</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="1">
         <v>45922</v>
       </c>
       <c r="B286" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C286">
-        <v>100.90900000000001</v>
+        <v>100.909</v>
       </c>
       <c r="D286">
-        <v>99.181700000000006</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A287" s="2">
+        <v>99.18170000000001</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="1">
         <v>45923</v>
       </c>
       <c r="B287" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C287">
         <v>100.1948</v>
       </c>
       <c r="D287">
-        <v>99.115200000000002</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A288" s="2">
+        <v>99.1152</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="1">
         <v>45924</v>
       </c>
       <c r="B288" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C288">
         <v>100.937</v>
       </c>
       <c r="D288">
-        <v>98.064599999999999</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A289" s="2">
+        <v>98.0646</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="1">
         <v>45925</v>
       </c>
       <c r="B289" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C289">
         <v>101.5073</v>
       </c>
       <c r="D289">
-        <v>97.917000000000002</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A290" s="2">
+        <v>97.917</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="1">
         <v>45926</v>
       </c>
       <c r="B290" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C290">
         <v>101.9177</v>
       </c>
       <c r="D290">
-        <v>97.747500000000002</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A291" s="2">
+        <v>97.7475</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="1">
         <v>45929</v>
       </c>
       <c r="B291" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C291">
-        <v>103.00069999999999</v>
+        <v>103.0007</v>
       </c>
       <c r="D291">
-        <v>97.968199999999996</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A292" s="2">
+        <v>97.9682</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="1">
         <v>45930</v>
       </c>
       <c r="B292" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C292">
         <v>103.5791</v>
       </c>
       <c r="D292">
-        <v>97.572100000000006</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A293" s="2">
+        <v>97.57210000000001</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="1">
         <v>45931</v>
       </c>
       <c r="B293" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C293">
         <v>104.2492</v>
       </c>
       <c r="D293">
-        <v>97.979200000000006</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A294" s="2">
+        <v>97.97920000000001</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="1">
         <v>45932</v>
       </c>
       <c r="B294" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C294">
         <v>104.8359</v>
       </c>
       <c r="D294">
-        <v>98.812200000000004</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A295" s="2">
+        <v>98.8122</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="1">
         <v>45933</v>
       </c>
       <c r="B295" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C295">
         <v>105.1728</v>
       </c>
       <c r="D295">
-        <v>98.974599999999995</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A296" s="2">
+        <v>98.9746</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="1">
         <v>45936</v>
       </c>
       <c r="B296" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C296">
-        <v>103.68819999999999</v>
+        <v>103.6882</v>
       </c>
       <c r="D296">
-        <v>99.292699999999996</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A297" s="2">
+        <v>99.2927</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="1">
         <v>45937</v>
       </c>
       <c r="B297" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C297">
         <v>103.8039</v>
       </c>
       <c r="D297">
-        <v>99.374700000000004</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A298" s="2">
+        <v>99.3747</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="1">
         <v>45938</v>
       </c>
       <c r="B298" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C298">
         <v>103.3779</v>
       </c>
       <c r="D298">
-        <v>99.414500000000004</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A299" s="2">
+        <v>99.4145</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="1">
         <v>45939</v>
       </c>
       <c r="B299" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C299">
-        <v>102.34350000000001</v>
+        <v>102.3435</v>
       </c>
       <c r="D299">
-        <v>98.880399999999995</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A300" s="2">
+        <v>98.88039999999999</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="1">
         <v>45940</v>
       </c>
       <c r="B300" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C300">
-        <v>103.79179999999999</v>
+        <v>103.7918</v>
       </c>
       <c r="D300">
-        <v>99.170299999999997</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A301" s="2">
+        <v>99.1703</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="1">
         <v>45943</v>
       </c>
       <c r="B301" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C301">
         <v>105.3005</v>
       </c>
       <c r="D301">
-        <v>99.132800000000003</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A302" s="2">
+        <v>99.1328</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="1">
         <v>45944</v>
       </c>
       <c r="B302" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C302">
         <v>106.5136</v>
       </c>
       <c r="D302">
-        <v>100.83240000000001</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A303" s="2">
+        <v>100.8324</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="1">
         <v>45945</v>
       </c>
       <c r="B303" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C303">
-        <v>106.78149999999999</v>
+        <v>106.7815</v>
       </c>
       <c r="D303">
-        <v>102.14190000000001</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A304" s="2">
+        <v>102.1419</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="1">
         <v>45946</v>
       </c>
       <c r="B304" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C304">
-        <v>108.00409999999999</v>
+        <v>108.0041</v>
       </c>
       <c r="D304">
-        <v>102.49809999999999</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A305" s="2">
+        <v>102.4981</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="1">
         <v>45947</v>
       </c>
       <c r="B305" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C305">
         <v>108.0615</v>
@@ -4692,12 +4640,12 @@
         <v>101.9134</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A306" s="2">
+    <row r="306" spans="1:4">
+      <c r="A306" s="1">
         <v>45950</v>
       </c>
       <c r="B306" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C306">
         <v>108.2871</v>
@@ -4706,12 +4654,12 @@
         <v>101.0472</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A307" s="2">
+    <row r="307" spans="1:4">
+      <c r="A307" s="1">
         <v>45951</v>
       </c>
       <c r="B307" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C307">
         <v>107.3682</v>
@@ -4720,12 +4668,12 @@
         <v>102.0505</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A308" s="2">
+    <row r="308" spans="1:4">
+      <c r="A308" s="1">
         <v>45952</v>
       </c>
       <c r="B308" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C308">
         <v>107.7624</v>
@@ -4734,12 +4682,12 @@
         <v>102.3058</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A309" s="2">
+    <row r="309" spans="1:4">
+      <c r="A309" s="1">
         <v>45953</v>
       </c>
       <c r="B309" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C309">
         <v>107.8621</v>
@@ -4748,54 +4696,54 @@
         <v>102.7397</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A310" s="2">
+    <row r="310" spans="1:4">
+      <c r="A310" s="1">
         <v>45954</v>
       </c>
       <c r="B310" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C310">
         <v>106.7628</v>
       </c>
       <c r="D310">
-        <v>101.34690000000001</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A311" s="2">
+        <v>101.3469</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="1">
         <v>45957</v>
       </c>
       <c r="B311" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C311">
         <v>106.7645</v>
       </c>
       <c r="D311">
-        <v>102.13939999999999</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A312" s="2">
+        <v>102.1394</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="1">
         <v>45958</v>
       </c>
       <c r="B312" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C312">
         <v>106.7413</v>
       </c>
       <c r="D312">
-        <v>102.55159999999999</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A313" s="2">
+        <v>102.5516</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" s="1">
         <v>45959</v>
       </c>
       <c r="B313" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C313">
         <v>108.3526</v>
@@ -4804,26 +4752,26 @@
         <v>101.6816</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A314" s="2">
+    <row r="314" spans="1:4">
+      <c r="A314" s="1">
         <v>45960</v>
       </c>
       <c r="B314" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C314">
-        <v>109.18980000000001</v>
+        <v>109.1898</v>
       </c>
       <c r="D314">
         <v>101.3387</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A315" s="2">
+    <row r="315" spans="1:4">
+      <c r="A315" s="1">
         <v>45961</v>
       </c>
       <c r="B315" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C315">
         <v>109.2473</v>
@@ -4832,12 +4780,12 @@
         <v>101.593</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A316" s="2">
+    <row r="316" spans="1:4">
+      <c r="A316" s="1">
         <v>45964</v>
       </c>
       <c r="B316" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C316">
         <v>109.5163</v>
@@ -4846,54 +4794,54 @@
         <v>101.6763</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A317" s="2">
+    <row r="317" spans="1:4">
+      <c r="A317" s="1">
         <v>45965</v>
       </c>
       <c r="B317" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C317">
         <v>109.6033</v>
       </c>
       <c r="D317">
-        <v>101.47929999999999</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A318" s="2">
+        <v>101.4793</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" s="1">
         <v>45966</v>
       </c>
       <c r="B318" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C318">
-        <v>109.46939999999999</v>
+        <v>109.4694</v>
       </c>
       <c r="D318">
         <v>101.4359</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A319" s="2">
+    <row r="319" spans="1:4">
+      <c r="A319" s="1">
         <v>45967</v>
       </c>
       <c r="B319" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C319">
-        <v>108.55029999999999</v>
+        <v>108.5503</v>
       </c>
       <c r="D319">
-        <v>101.27200000000001</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A320" s="2">
+        <v>101.272</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" s="1">
         <v>45968</v>
       </c>
       <c r="B320" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C320">
         <v>108.4636</v>
@@ -4902,12 +4850,12 @@
         <v>101.4361</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A321" s="2">
+    <row r="321" spans="1:4">
+      <c r="A321" s="1">
         <v>45971</v>
       </c>
       <c r="B321" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C321">
         <v>107.8505</v>
@@ -4916,26 +4864,26 @@
         <v>102.6708</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A322" s="2">
+    <row r="322" spans="1:4">
+      <c r="A322" s="1">
         <v>45972</v>
       </c>
       <c r="B322" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C322">
-        <v>106.79730000000001</v>
+        <v>106.7973</v>
       </c>
       <c r="D322">
         <v>100.6037</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A323" s="2">
+    <row r="323" spans="1:4">
+      <c r="A323" s="1">
         <v>45973</v>
       </c>
       <c r="B323" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C323">
         <v>107.2889</v>
@@ -4944,12 +4892,12 @@
         <v>100.4533</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A324" s="2">
+    <row r="324" spans="1:4">
+      <c r="A324" s="1">
         <v>45974</v>
       </c>
       <c r="B324" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C324">
         <v>107.6778</v>
@@ -4958,26 +4906,26 @@
         <v>100.6353</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A325" s="2">
+    <row r="325" spans="1:4">
+      <c r="A325" s="1">
         <v>45975</v>
       </c>
       <c r="B325" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C325">
-        <v>106.15519999999999</v>
+        <v>106.1552</v>
       </c>
       <c r="D325">
         <v>100.9139</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A326" s="2">
+    <row r="326" spans="1:4">
+      <c r="A326" s="1">
         <v>45978</v>
       </c>
       <c r="B326" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C326">
         <v>106.095</v>
@@ -4986,68 +4934,68 @@
         <v>100.654</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A327" s="2">
+    <row r="327" spans="1:4">
+      <c r="A327" s="1">
         <v>45979</v>
       </c>
       <c r="B327" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C327">
         <v>107.0026</v>
       </c>
       <c r="D327">
-        <v>99.279700000000005</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A328" s="2">
+        <v>99.27970000000001</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" s="1">
         <v>45980</v>
       </c>
       <c r="B328" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C328">
         <v>107.9734</v>
       </c>
       <c r="D328">
-        <v>99.579899999999995</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A329" s="2">
+        <v>99.57989999999999</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" s="1">
         <v>45981</v>
       </c>
       <c r="B329" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C329">
-        <v>108.92359999999999</v>
+        <v>108.9236</v>
       </c>
       <c r="D329">
         <v>100.9958</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A330" s="2">
+    <row r="330" spans="1:4">
+      <c r="A330" s="1">
         <v>45982</v>
       </c>
       <c r="B330" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C330">
-        <v>109.00539999999999</v>
+        <v>109.0054</v>
       </c>
       <c r="D330">
-        <v>99.796899999999994</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A331" s="2">
+        <v>99.79689999999999</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" s="1">
         <v>45985</v>
       </c>
       <c r="B331" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C331">
         <v>108.3013</v>
@@ -5056,96 +5004,96 @@
         <v>100.5265</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A332" s="2">
+    <row r="332" spans="1:4">
+      <c r="A332" s="1">
         <v>45986</v>
       </c>
       <c r="B332" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C332">
         <v>107.3909</v>
       </c>
       <c r="D332">
-        <v>100.30249999999999</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A333" s="2">
+        <v>100.3025</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" s="1">
         <v>45987</v>
       </c>
       <c r="B333" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C333">
         <v>107.7393</v>
       </c>
       <c r="D333">
-        <v>100.29340000000001</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A334" s="2">
+        <v>100.2934</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" s="1">
         <v>45988</v>
       </c>
       <c r="B334" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C334">
         <v>108.1193</v>
       </c>
       <c r="D334">
-        <v>99.488699999999994</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A335" s="2">
+        <v>99.48869999999999</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" s="1">
         <v>45989</v>
       </c>
       <c r="B335" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C335">
         <v>109.3014</v>
       </c>
       <c r="D335">
-        <v>99.262299999999996</v>
-      </c>
-    </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A336" s="2">
+        <v>99.2623</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" s="1">
         <v>45992</v>
       </c>
       <c r="B336" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C336">
-        <v>110.32940000000001</v>
+        <v>110.3294</v>
       </c>
       <c r="D336">
         <v>100.3344</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A337" s="2">
+    <row r="337" spans="1:4">
+      <c r="A337" s="1">
         <v>45993</v>
       </c>
       <c r="B337" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C337">
         <v>110.2582</v>
       </c>
       <c r="D337">
-        <v>100.84220000000001</v>
-      </c>
-    </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A338" s="2">
+        <v>100.8422</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" s="1">
         <v>45994</v>
       </c>
       <c r="B338" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C338">
         <v>109.187</v>
@@ -5154,26 +5102,26 @@
         <v>102.2801</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A339" s="2">
+    <row r="339" spans="1:4">
+      <c r="A339" s="1">
         <v>45995</v>
       </c>
       <c r="B339" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C339">
-        <v>108.95010000000001</v>
+        <v>108.9501</v>
       </c>
       <c r="D339">
-        <v>103.28440000000001</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A340" s="2">
+        <v>103.2844</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" s="1">
         <v>45996</v>
       </c>
       <c r="B340" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C340">
         <v>109.1904</v>
@@ -5182,54 +5130,54 @@
         <v>103.6885</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A341" s="2">
+    <row r="341" spans="1:4">
+      <c r="A341" s="1">
         <v>45999</v>
       </c>
       <c r="B341" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C341">
         <v>109.0577</v>
       </c>
       <c r="D341">
-        <v>105.17659999999999</v>
-      </c>
-    </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A342" s="2">
+        <v>105.1766</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342" s="1">
         <v>46000</v>
       </c>
       <c r="B342" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C342">
         <v>108.5909</v>
       </c>
       <c r="D342">
-        <v>105.58799999999999</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A343" s="2">
+        <v>105.588</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" s="1">
         <v>46001</v>
       </c>
       <c r="B343" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C343">
-        <v>108.86190000000001</v>
+        <v>108.8619</v>
       </c>
       <c r="D343">
         <v>106.3297</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A344" s="2">
+    <row r="344" spans="1:4">
+      <c r="A344" s="1">
         <v>46002</v>
       </c>
       <c r="B344" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C344">
         <v>108.4616</v>
@@ -5238,12 +5186,12 @@
         <v>106.1199</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A345" s="2">
+    <row r="345" spans="1:4">
+      <c r="A345" s="1">
         <v>46003</v>
       </c>
       <c r="B345" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C345">
         <v>107.9529</v>
@@ -5252,12 +5200,12 @@
         <v>106.2189</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A346" s="2">
+    <row r="346" spans="1:4">
+      <c r="A346" s="1">
         <v>46006</v>
       </c>
       <c r="B346" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C346">
         <v>108.274</v>
@@ -5266,12 +5214,12 @@
         <v>105.6687</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A347" s="2">
+    <row r="347" spans="1:4">
+      <c r="A347" s="1">
         <v>46007</v>
       </c>
       <c r="B347" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C347">
         <v>107.9658</v>
@@ -5280,26 +5228,26 @@
         <v>106.5475</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A348" s="2">
+    <row r="348" spans="1:4">
+      <c r="A348" s="1">
         <v>46008</v>
       </c>
       <c r="B348" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C348">
         <v>108.2276</v>
       </c>
       <c r="D348">
-        <v>105.58580000000001</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A349" s="2">
+        <v>105.5858</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" s="1">
         <v>46009</v>
       </c>
       <c r="B349" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C349">
         <v>108.5157</v>
@@ -5308,40 +5256,40 @@
         <v>106.2889</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A350" s="2">
+    <row r="350" spans="1:4">
+      <c r="A350" s="1">
         <v>46010</v>
       </c>
       <c r="B350" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C350">
-        <v>107.55410000000001</v>
+        <v>107.5541</v>
       </c>
       <c r="D350">
-        <v>106.16930000000001</v>
-      </c>
-    </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A351" s="2">
+        <v>106.1693</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" s="1">
         <v>46013</v>
       </c>
       <c r="B351" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C351">
         <v>107.1785</v>
       </c>
       <c r="D351">
-        <v>107.20650000000001</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A352" s="2">
+        <v>107.2065</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" s="1">
         <v>46014</v>
       </c>
       <c r="B352" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C352">
         <v>108.4819</v>
@@ -5350,68 +5298,68 @@
         <v>107.8934</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A353" s="2">
+    <row r="353" spans="1:4">
+      <c r="A353" s="1">
         <v>46015</v>
       </c>
       <c r="B353" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C353">
-        <v>107.50060000000001</v>
+        <v>107.5006</v>
       </c>
       <c r="D353">
         <v>109.5081</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A354" s="2">
+    <row r="354" spans="1:4">
+      <c r="A354" s="1">
         <v>46016</v>
       </c>
       <c r="B354" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C354">
-        <v>105.69119999999999</v>
+        <v>105.6912</v>
       </c>
       <c r="D354">
         <v>110.1921</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A355" s="2">
+    <row r="355" spans="1:4">
+      <c r="A355" s="1">
         <v>46017</v>
       </c>
       <c r="B355" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C355">
-        <v>104.13200000000001</v>
+        <v>104.132</v>
       </c>
       <c r="D355">
         <v>108.8503</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A356" s="2">
+    <row r="356" spans="1:4">
+      <c r="A356" s="1">
         <v>46020</v>
       </c>
       <c r="B356" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C356">
-        <v>104.20180000000001</v>
+        <v>104.2018</v>
       </c>
       <c r="D356">
         <v>108.8356</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A357" s="2">
+    <row r="357" spans="1:4">
+      <c r="A357" s="1">
         <v>46021</v>
       </c>
       <c r="B357" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C357">
         <v>104.2732</v>
@@ -5420,12 +5368,12 @@
         <v>107.8586</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A358" s="2">
+    <row r="358" spans="1:4">
+      <c r="A358" s="1">
         <v>46022</v>
       </c>
       <c r="B358" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C358">
         <v>104.2184</v>
@@ -5434,12 +5382,12 @@
         <v>107.4546</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A359" s="2">
+    <row r="359" spans="1:4">
+      <c r="A359" s="1">
         <v>46023</v>
       </c>
       <c r="B359" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C359">
         <v>105.2957</v>
@@ -5448,12 +5396,12 @@
         <v>108.7967</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A360" s="2">
+    <row r="360" spans="1:4">
+      <c r="A360" s="1">
         <v>46024</v>
       </c>
       <c r="B360" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C360">
         <v>103.0457</v>
@@ -5462,26 +5410,26 @@
         <v>109.3951</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A361" s="2">
+    <row r="361" spans="1:4">
+      <c r="A361" s="1">
         <v>46027</v>
       </c>
       <c r="B361" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C361">
-        <v>103.42310000000001</v>
+        <v>103.4231</v>
       </c>
       <c r="D361">
         <v>108.8272</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A362" s="2">
+    <row r="362" spans="1:4">
+      <c r="A362" s="1">
         <v>46028</v>
       </c>
       <c r="B362" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C362">
         <v>104.7851</v>
@@ -5490,40 +5438,40 @@
         <v>107.9881</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A363" s="2">
+    <row r="363" spans="1:4">
+      <c r="A363" s="1">
         <v>46029</v>
       </c>
       <c r="B363" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C363">
-        <v>103.86660000000001</v>
+        <v>103.8666</v>
       </c>
       <c r="D363">
-        <v>108.05970000000001</v>
-      </c>
-    </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A364" s="2">
+        <v>108.0597</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" s="1">
         <v>46030</v>
       </c>
       <c r="B364" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C364">
         <v>103.5899</v>
       </c>
       <c r="D364">
-        <v>107.05119999999999</v>
-      </c>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A365" s="2">
+        <v>107.0512</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" s="1">
         <v>46031</v>
       </c>
       <c r="B365" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C365">
         <v>102.9986</v>
@@ -5532,26 +5480,26 @@
         <v>106.5192</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A366" s="2">
+    <row r="366" spans="1:4">
+      <c r="A366" s="1">
         <v>46034</v>
       </c>
       <c r="B366" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C366">
-        <v>102.29179999999999</v>
+        <v>102.2918</v>
       </c>
       <c r="D366">
-        <v>106.82769999999999</v>
-      </c>
-    </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A367" s="2">
+        <v>106.8277</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" s="1">
         <v>46035</v>
       </c>
       <c r="B367" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C367">
         <v>102.0639</v>
@@ -5560,54 +5508,54 @@
         <v>107.8578</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A368" s="2">
+    <row r="368" spans="1:4">
+      <c r="A368" s="1">
         <v>46036</v>
       </c>
       <c r="B368" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C368">
-        <v>103.29649999999999</v>
+        <v>103.2965</v>
       </c>
       <c r="D368">
-        <v>108.42619999999999</v>
-      </c>
-    </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A369" s="2">
+        <v>108.4262</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" s="1">
         <v>46037</v>
       </c>
       <c r="B369" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C369">
-        <v>104.88939999999999</v>
+        <v>104.8894</v>
       </c>
       <c r="D369">
         <v>106.4821</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A370" s="2">
+    <row r="370" spans="1:4">
+      <c r="A370" s="1">
         <v>46038</v>
       </c>
       <c r="B370" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C370">
         <v>104.6474</v>
       </c>
       <c r="D370">
-        <v>106.78400000000001</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A371" s="2">
+        <v>106.784</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" s="1">
         <v>46041</v>
       </c>
       <c r="B371" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C371">
         <v>106.3189</v>
@@ -5616,40 +5564,40 @@
         <v>106.8882</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A372" s="2">
+    <row r="372" spans="1:4">
+      <c r="A372" s="1">
         <v>46042</v>
       </c>
       <c r="B372" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C372">
-        <v>106.39579999999999</v>
+        <v>106.3958</v>
       </c>
       <c r="D372">
-        <v>107.28489999999999</v>
-      </c>
-    </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A373" s="2">
+        <v>107.2849</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" s="1">
         <v>46043</v>
       </c>
       <c r="B373" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C373">
-        <v>107.96380000000001</v>
+        <v>107.9638</v>
       </c>
       <c r="D373">
         <v>108.715</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A374" s="2">
+    <row r="374" spans="1:4">
+      <c r="A374" s="1">
         <v>46044</v>
       </c>
       <c r="B374" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C374">
         <v>107.9284</v>
@@ -5658,40 +5606,40 @@
         <v>106.964</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A375" s="2">
+    <row r="375" spans="1:4">
+      <c r="A375" s="1">
         <v>46045</v>
       </c>
       <c r="B375" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C375">
-        <v>108.09050000000001</v>
+        <v>108.0905</v>
       </c>
       <c r="D375">
         <v>106.501</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A376" s="2">
+    <row r="376" spans="1:4">
+      <c r="A376" s="1">
         <v>46048</v>
       </c>
       <c r="B376" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C376">
-        <v>108.45959999999999</v>
+        <v>108.4596</v>
       </c>
       <c r="D376">
         <v>107.0471</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A377" s="2">
+    <row r="377" spans="1:4">
+      <c r="A377" s="1">
         <v>46049</v>
       </c>
       <c r="B377" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C377">
         <v>111.3188</v>
@@ -5700,12 +5648,12 @@
         <v>105.7354</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A378" s="2">
+    <row r="378" spans="1:4">
+      <c r="A378" s="1">
         <v>46050</v>
       </c>
       <c r="B378" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C378">
         <v>112.14</v>
@@ -5714,12 +5662,12 @@
         <v>107.0262</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A379" s="2">
+    <row r="379" spans="1:4">
+      <c r="A379" s="1">
         <v>46051</v>
       </c>
       <c r="B379" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C379">
         <v>111.5416</v>
@@ -5728,26 +5676,26 @@
         <v>107.3844</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A380" s="2">
+    <row r="380" spans="1:4">
+      <c r="A380" s="1">
         <v>46052</v>
       </c>
       <c r="B380" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C380">
-        <v>112.47150000000001</v>
+        <v>112.4715</v>
       </c>
       <c r="D380">
         <v>108.1546</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A381" s="2">
+    <row r="381" spans="1:4">
+      <c r="A381" s="1">
         <v>46055</v>
       </c>
       <c r="B381" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C381">
         <v>112.1883</v>
@@ -5756,40 +5704,40 @@
         <v>107.7039</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A382" s="2">
+    <row r="382" spans="1:4">
+      <c r="A382" s="1">
         <v>46056</v>
       </c>
       <c r="B382" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C382">
-        <v>111.78879999999999</v>
+        <v>111.7888</v>
       </c>
       <c r="D382">
         <v>108.4482</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A383" s="2">
+    <row r="383" spans="1:4">
+      <c r="A383" s="1">
         <v>46057</v>
       </c>
       <c r="B383" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C383">
         <v>112.6657</v>
       </c>
       <c r="D383">
-        <v>109.41849999999999</v>
-      </c>
-    </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A384" s="2">
+        <v>109.4185</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" s="1">
         <v>46058</v>
       </c>
       <c r="B384" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C384">
         <v>112.7431</v>
@@ -5798,26 +5746,26 @@
         <v>109.6661</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A385" s="2">
+    <row r="385" spans="1:4">
+      <c r="A385" s="1">
         <v>46059</v>
       </c>
       <c r="B385" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C385">
-        <v>113.04810000000001</v>
+        <v>113.0481</v>
       </c>
       <c r="D385">
         <v>109.9157</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A386" s="2">
+    <row r="386" spans="1:4">
+      <c r="A386" s="1">
         <v>46062</v>
       </c>
       <c r="B386" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C386">
         <v>113.11</v>
@@ -5826,12 +5774,12 @@
         <v>110.1973</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A387" s="2">
+    <row r="387" spans="1:4">
+      <c r="A387" s="1">
         <v>46063</v>
       </c>
       <c r="B387" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C387">
         <v>113.4695</v>
@@ -5840,40 +5788,40 @@
         <v>109.4803</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A388" s="2">
+    <row r="388" spans="1:4">
+      <c r="A388" s="1">
         <v>46064</v>
       </c>
       <c r="B388" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C388">
-        <v>113.91200000000001</v>
+        <v>113.912</v>
       </c>
       <c r="D388">
-        <v>109.39490000000001</v>
-      </c>
-    </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A389" s="2">
+        <v>109.3949</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
+      <c r="A389" s="1">
         <v>46065</v>
       </c>
       <c r="B389" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C389">
-        <v>112.16160000000001</v>
+        <v>112.1616</v>
       </c>
       <c r="D389">
         <v>109.3052</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A390" s="2">
+    <row r="390" spans="1:4">
+      <c r="A390" s="1">
         <v>46066</v>
       </c>
       <c r="B390" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C390">
         <v>112.82</v>
@@ -5882,12 +5830,12 @@
         <v>109.6841</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A391" s="2">
+    <row r="391" spans="1:4">
+      <c r="A391" s="1">
         <v>46069</v>
       </c>
       <c r="B391" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C391">
         <v>111.9652</v>
@@ -5896,12 +5844,12 @@
         <v>110.6053</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A392" s="2">
+    <row r="392" spans="1:4">
+      <c r="A392" s="1">
         <v>46070</v>
       </c>
       <c r="B392" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C392">
         <v>110.6965</v>
@@ -5910,26 +5858,26 @@
         <v>109.7129</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A393" s="2">
+    <row r="393" spans="1:4">
+      <c r="A393" s="1">
         <v>46071</v>
       </c>
       <c r="B393" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C393">
         <v>110.6918</v>
       </c>
       <c r="D393">
-        <v>109.64709999999999</v>
-      </c>
-    </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A394" s="2">
+        <v>109.6471</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
+      <c r="A394" s="1">
         <v>46072</v>
       </c>
       <c r="B394" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C394">
         <v>110.8155</v>
@@ -5938,12 +5886,12 @@
         <v>110.9905</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A395" s="2">
+    <row r="395" spans="1:4">
+      <c r="A395" s="1">
         <v>46073</v>
       </c>
       <c r="B395" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C395">
         <v>110.2367</v>
@@ -5952,12 +5900,12 @@
         <v>110.3746</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A396" s="2">
+    <row r="396" spans="1:4">
+      <c r="A396" s="1">
         <v>46076</v>
       </c>
       <c r="B396" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C396">
         <v>111.0317</v>
@@ -5966,12 +5914,12 @@
         <v>109.6927</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A397" s="2">
+    <row r="397" spans="1:4">
+      <c r="A397" s="1">
         <v>46077</v>
       </c>
       <c r="B397" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C397">
         <v>109.8643</v>
@@ -5980,26 +5928,26 @@
         <v>109.9141</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A398" s="2">
+    <row r="398" spans="1:4">
+      <c r="A398" s="1">
         <v>46078</v>
       </c>
       <c r="B398" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C398">
         <v>109.5472</v>
       </c>
       <c r="D398">
-        <v>110.70059999999999</v>
-      </c>
-    </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A399" s="2">
+        <v>110.7006</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
+      <c r="A399" s="1">
         <v>46079</v>
       </c>
       <c r="B399" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C399">
         <v>109.072</v>
@@ -6008,12 +5956,12 @@
         <v>110.755</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A400" s="2">
+    <row r="400" spans="1:4">
+      <c r="A400" s="1">
         <v>46080</v>
       </c>
       <c r="B400" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C400">
         <v>109.0778</v>
@@ -6022,12 +5970,12 @@
         <v>111.9768</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A401" s="2">
+    <row r="401" spans="1:4">
+      <c r="A401" s="1">
         <v>46083</v>
       </c>
       <c r="B401" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C401">
         <v>109.3732</v>
@@ -6036,12 +5984,12 @@
         <v>112.7891</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A402" s="2">
+    <row r="402" spans="1:4">
+      <c r="A402" s="1">
         <v>46084</v>
       </c>
       <c r="B402" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C402">
         <v>108.5214</v>
@@ -6050,26 +5998,26 @@
         <v>113.5938</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A403" s="2">
+    <row r="403" spans="1:4">
+      <c r="A403" s="1">
         <v>46085</v>
       </c>
       <c r="B403" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C403">
-        <v>109.20959999999999</v>
+        <v>109.2096</v>
       </c>
       <c r="D403">
-        <v>114.14279999999999</v>
-      </c>
-    </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A404" s="2">
+        <v>114.1428</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4">
+      <c r="A404" s="1">
         <v>46086</v>
       </c>
       <c r="B404" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C404">
         <v>109.313</v>
@@ -6078,12 +6026,12 @@
         <v>116.3139</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A405" s="2">
+    <row r="405" spans="1:4">
+      <c r="A405" s="1">
         <v>46087</v>
       </c>
       <c r="B405" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C405">
         <v>107.6734</v>
@@ -6092,12 +6040,12 @@
         <v>116.1695</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A406" s="2">
+    <row r="406" spans="1:4">
+      <c r="A406" s="1">
         <v>46090</v>
       </c>
       <c r="B406" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C406">
         <v>106</v>
@@ -6106,12 +6054,12 @@
         <v>114.354</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A407" s="2">
+    <row r="407" spans="1:4">
+      <c r="A407" s="1">
         <v>46091</v>
       </c>
       <c r="B407" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C407">
         <v>106.0352</v>
@@ -6120,26 +6068,26 @@
         <v>115.8674</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A408" s="2">
+    <row r="408" spans="1:4">
+      <c r="A408" s="1">
         <v>46092</v>
       </c>
       <c r="B408" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C408">
         <v>105.8901</v>
       </c>
       <c r="D408">
-        <v>115.48950000000001</v>
-      </c>
-    </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A409" s="2">
+        <v>115.4895</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
+      <c r="A409" s="1">
         <v>46093</v>
       </c>
       <c r="B409" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C409">
         <v>105.8466</v>
@@ -6148,12 +6096,12 @@
         <v>115.6354</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A410" s="2">
+    <row r="410" spans="1:4">
+      <c r="A410" s="1">
         <v>46094</v>
       </c>
       <c r="B410" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C410">
         <v>105.8683</v>
@@ -6162,26 +6110,26 @@
         <v>116.893</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A411" s="2">
+    <row r="411" spans="1:4">
+      <c r="A411" s="1">
         <v>46097</v>
       </c>
       <c r="B411" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C411">
-        <v>106.10890000000001</v>
+        <v>106.1089</v>
       </c>
       <c r="D411">
         <v>115.4415</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A412" s="2">
+    <row r="412" spans="1:4">
+      <c r="A412" s="1">
         <v>46098</v>
       </c>
       <c r="B412" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C412">
         <v>106.9751</v>
@@ -6190,12 +6138,12 @@
         <v>114.3317</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A413" s="2">
+    <row r="413" spans="1:4">
+      <c r="A413" s="1">
         <v>46099</v>
       </c>
       <c r="B413" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C413">
         <v>106.0519</v>
@@ -6204,26 +6152,26 @@
         <v>112.9128</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A414" s="2">
+    <row r="414" spans="1:4">
+      <c r="A414" s="1">
         <v>46100</v>
       </c>
       <c r="B414" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C414">
-        <v>105.08410000000001</v>
+        <v>105.0841</v>
       </c>
       <c r="D414">
         <v>112.2406</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A415" s="2">
+    <row r="415" spans="1:4">
+      <c r="A415" s="1">
         <v>46101</v>
       </c>
       <c r="B415" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C415">
         <v>104.1925</v>
@@ -6232,12 +6180,12 @@
         <v>112.6803</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A416" s="2">
+    <row r="416" spans="1:4">
+      <c r="A416" s="1">
         <v>46104</v>
       </c>
       <c r="B416" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C416">
         <v>104.4832</v>
@@ -6246,26 +6194,26 @@
         <v>113.1979</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A417" s="2">
+    <row r="417" spans="1:4">
+      <c r="A417" s="1">
         <v>46105</v>
       </c>
       <c r="B417" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C417">
         <v>105.5894</v>
       </c>
       <c r="D417">
-        <v>113.49339999999999</v>
-      </c>
-    </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A418" s="2">
+        <v>113.4934</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4">
+      <c r="A418" s="1">
         <v>46106</v>
       </c>
       <c r="B418" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C418">
         <v>105.2637</v>
@@ -6274,12 +6222,12 @@
         <v>112.256</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A419" s="2">
+    <row r="419" spans="1:4">
+      <c r="A419" s="1">
         <v>46107</v>
       </c>
       <c r="B419" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C419">
         <v>103.1613</v>
@@ -6288,12 +6236,12 @@
         <v>110.2264</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A420" s="2">
+    <row r="420" spans="1:4">
+      <c r="A420" s="1">
         <v>46108</v>
       </c>
       <c r="B420" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C420">
         <v>101.7722</v>
@@ -6302,26 +6250,26 @@
         <v>110.3184</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A421" s="2">
+    <row r="421" spans="1:4">
+      <c r="A421" s="1">
         <v>46111</v>
       </c>
       <c r="B421" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C421">
-        <v>101.12479999999999</v>
+        <v>101.1248</v>
       </c>
       <c r="D421">
         <v>109.9461</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A422" s="2">
+    <row r="422" spans="1:4">
+      <c r="A422" s="1">
         <v>46112</v>
       </c>
       <c r="B422" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C422">
         <v>100.7085</v>
@@ -6330,26 +6278,26 @@
         <v>110.3942</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A423" s="2">
+    <row r="423" spans="1:4">
+      <c r="A423" s="1">
         <v>46113</v>
       </c>
       <c r="B423" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C423">
-        <v>100.41670000000001</v>
+        <v>100.4167</v>
       </c>
       <c r="D423">
         <v>111.0583</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A424" s="2">
+    <row r="424" spans="1:4">
+      <c r="A424" s="1">
         <v>46114</v>
       </c>
       <c r="B424" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C424">
         <v>100.4918</v>
@@ -6358,26 +6306,26 @@
         <v>111.2255</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A425" s="2">
+    <row r="425" spans="1:4">
+      <c r="A425" s="1">
         <v>46115</v>
       </c>
       <c r="B425" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C425">
-        <v>100.27979999999999</v>
+        <v>100.2798</v>
       </c>
       <c r="D425">
         <v>111.9464</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A426" s="2">
+    <row r="426" spans="1:4">
+      <c r="A426" s="1">
         <v>46118</v>
       </c>
       <c r="B426" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C426">
         <v>101.1816</v>
@@ -6386,12 +6334,12 @@
         <v>112.1964</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A427" s="2">
+    <row r="427" spans="1:4">
+      <c r="A427" s="1">
         <v>46119</v>
       </c>
       <c r="B427" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C427">
         <v>100.6675</v>
@@ -6400,12 +6348,12 @@
         <v>112.7171</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A428" s="2">
+    <row r="428" spans="1:4">
+      <c r="A428" s="1">
         <v>46120</v>
       </c>
       <c r="B428" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C428">
         <v>100.003</v>
@@ -6414,82 +6362,82 @@
         <v>112.1267</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A429" s="2">
+    <row r="429" spans="1:4">
+      <c r="A429" s="1">
         <v>46121</v>
       </c>
       <c r="B429" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C429">
         <v>100.437</v>
       </c>
       <c r="D429">
-        <v>112.01049999999999</v>
-      </c>
-    </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A430" s="2">
+        <v>112.0105</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4">
+      <c r="A430" s="1">
         <v>46122</v>
       </c>
       <c r="B430" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C430">
-        <v>99.222499999999997</v>
+        <v>99.2225</v>
       </c>
       <c r="D430">
         <v>112.2316</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A431" s="2">
+    <row r="431" spans="1:4">
+      <c r="A431" s="1">
         <v>46125</v>
       </c>
       <c r="B431" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C431">
-        <v>99.580799999999996</v>
+        <v>99.5808</v>
       </c>
       <c r="D431">
         <v>113.0132</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A432" s="2">
+    <row r="432" spans="1:4">
+      <c r="A432" s="1">
         <v>46126</v>
       </c>
       <c r="B432" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C432">
-        <v>99.707300000000004</v>
+        <v>99.7073</v>
       </c>
       <c r="D432">
         <v>112.7024</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A433" s="2">
+    <row r="433" spans="1:4">
+      <c r="A433" s="1">
         <v>46127</v>
       </c>
       <c r="B433" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C433">
-        <v>99.630600000000001</v>
+        <v>99.6306</v>
       </c>
       <c r="D433">
         <v>113.2174</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A434" s="2">
+    <row r="434" spans="1:4">
+      <c r="A434" s="1">
         <v>46128</v>
       </c>
       <c r="B434" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C434">
         <v>100.9644</v>
@@ -6498,26 +6446,26 @@
         <v>113.0219</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A435" s="2">
+    <row r="435" spans="1:4">
+      <c r="A435" s="1">
         <v>46129</v>
       </c>
       <c r="B435" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C435">
         <v>100.4958</v>
       </c>
       <c r="D435">
-        <v>112.96080000000001</v>
-      </c>
-    </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A436" s="2">
+        <v>112.9608</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4">
+      <c r="A436" s="1">
         <v>46132</v>
       </c>
       <c r="B436" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C436">
         <v>102.2281</v>
@@ -6526,26 +6474,26 @@
         <v>113.7557</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A437" s="2">
+    <row r="437" spans="1:4">
+      <c r="A437" s="1">
         <v>46133</v>
       </c>
       <c r="B437" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C437">
-        <v>102.08450000000001</v>
+        <v>102.0845</v>
       </c>
       <c r="D437">
-        <v>111.98739999999999</v>
-      </c>
-    </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A438" s="2">
+        <v>111.9874</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4">
+      <c r="A438" s="1">
         <v>46134</v>
       </c>
       <c r="B438" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C438">
         <v>101.0654</v>
@@ -6554,68 +6502,68 @@
         <v>110.8707</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A439" s="2">
+    <row r="439" spans="1:4">
+      <c r="A439" s="1">
         <v>46135</v>
       </c>
       <c r="B439" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C439">
-        <v>101.16679999999999</v>
+        <v>101.1668</v>
       </c>
       <c r="D439">
-        <v>109.60039999999999</v>
-      </c>
-    </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A440" s="2">
+        <v>109.6004</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4">
+      <c r="A440" s="1">
         <v>46136</v>
       </c>
       <c r="B440" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C440">
-        <v>100.32250000000001</v>
+        <v>100.3225</v>
       </c>
       <c r="D440">
         <v>107.5981</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A441" s="2">
+    <row r="441" spans="1:4">
+      <c r="A441" s="1">
         <v>46139</v>
       </c>
       <c r="B441" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C441">
-        <v>99.750799999999998</v>
+        <v>99.7508</v>
       </c>
       <c r="D441">
         <v>107.0573</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A442" s="2">
+    <row r="442" spans="1:4">
+      <c r="A442" s="1">
         <v>46140</v>
       </c>
       <c r="B442" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C442">
-        <v>100.11709999999999</v>
+        <v>100.1171</v>
       </c>
       <c r="D442">
         <v>107.742</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A443" s="2">
+    <row r="443" spans="1:4">
+      <c r="A443" s="1">
         <v>46141</v>
       </c>
       <c r="B443" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C443">
         <v>100.6142</v>
@@ -6624,26 +6572,26 @@
         <v>107.5395</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A444" s="2">
+    <row r="444" spans="1:4">
+      <c r="A444" s="1">
         <v>46142</v>
       </c>
       <c r="B444" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C444">
-        <v>100.14709999999999</v>
+        <v>100.1471</v>
       </c>
       <c r="D444">
         <v>107.7527</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A445" s="2">
+    <row r="445" spans="1:4">
+      <c r="A445" s="1">
         <v>46143</v>
       </c>
       <c r="B445" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C445">
         <v>100.9971</v>
@@ -6652,12 +6600,12 @@
         <v>108.7347</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A446" s="2">
+    <row r="446" spans="1:4">
+      <c r="A446" s="1">
         <v>46146</v>
       </c>
       <c r="B446" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C446">
         <v>101.9944</v>
@@ -6666,40 +6614,40 @@
         <v>109.9331</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A447" s="2">
+    <row r="447" spans="1:4">
+      <c r="A447" s="1">
         <v>46147</v>
       </c>
       <c r="B447" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C447">
-        <v>103.23350000000001</v>
+        <v>103.2335</v>
       </c>
       <c r="D447">
-        <v>109.91630000000001</v>
-      </c>
-    </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A448" s="2">
+        <v>109.9163</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4">
+      <c r="A448" s="1">
         <v>46148</v>
       </c>
       <c r="B448" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C448">
         <v>103.724</v>
       </c>
       <c r="D448">
-        <v>111.15049999999999</v>
-      </c>
-    </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A449" s="2">
+        <v>111.1505</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4">
+      <c r="A449" s="1">
         <v>46149</v>
       </c>
       <c r="B449" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C449">
         <v>104.9225</v>
@@ -6708,40 +6656,40 @@
         <v>111.2769</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A450" s="2">
+    <row r="450" spans="1:4">
+      <c r="A450" s="1">
         <v>46150</v>
       </c>
       <c r="B450" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C450">
         <v>103.3583</v>
       </c>
       <c r="D450">
-        <v>110.57599999999999</v>
-      </c>
-    </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A451" s="2">
+        <v>110.576</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4">
+      <c r="A451" s="1">
         <v>46153</v>
       </c>
       <c r="B451" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C451">
-        <v>103.13509999999999</v>
+        <v>103.1351</v>
       </c>
       <c r="D451">
-        <v>110.09439999999999</v>
-      </c>
-    </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A452" s="2">
+        <v>110.0944</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4">
+      <c r="A452" s="1">
         <v>46154</v>
       </c>
       <c r="B452" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C452">
         <v>102.4504</v>
@@ -6750,82 +6698,82 @@
         <v>108.8344</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A453" s="2">
+    <row r="453" spans="1:4">
+      <c r="A453" s="1">
         <v>46155</v>
       </c>
       <c r="B453" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C453">
-        <v>102.59439999999999</v>
+        <v>102.5944</v>
       </c>
       <c r="D453">
-        <v>108.10469999999999</v>
-      </c>
-    </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A454" s="2">
+        <v>108.1047</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4">
+      <c r="A454" s="1">
         <v>46156</v>
       </c>
       <c r="B454" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C454">
-        <v>102.16070000000001</v>
+        <v>102.1607</v>
       </c>
       <c r="D454">
         <v>107.8383</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A455" s="2">
+    <row r="455" spans="1:4">
+      <c r="A455" s="1">
         <v>46157</v>
       </c>
       <c r="B455" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C455">
         <v>102.0665</v>
       </c>
       <c r="D455">
-        <v>108.57470000000001</v>
-      </c>
-    </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A456" s="2">
+        <v>108.5747</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4">
+      <c r="A456" s="1">
         <v>46160</v>
       </c>
       <c r="B456" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C456">
         <v>103.6776</v>
       </c>
       <c r="D456">
-        <v>110.11279999999999</v>
-      </c>
-    </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A457" s="2">
+        <v>110.1128</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4">
+      <c r="A457" s="1">
         <v>46161</v>
       </c>
       <c r="B457" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C457">
-        <v>103.57899999999999</v>
+        <v>103.579</v>
       </c>
       <c r="D457">
         <v>108.9393</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A458" s="2">
+    <row r="458" spans="1:4">
+      <c r="A458" s="1">
         <v>46162</v>
       </c>
       <c r="B458" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C458">
         <v>103.9735</v>
@@ -6834,12 +6782,12 @@
         <v>109.3252</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A459" s="2">
+    <row r="459" spans="1:4">
+      <c r="A459" s="1">
         <v>46163</v>
       </c>
       <c r="B459" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C459">
         <v>103.8216</v>
@@ -6848,12 +6796,12 @@
         <v>108.4589</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A460" s="2">
+    <row r="460" spans="1:4">
+      <c r="A460" s="1">
         <v>46164</v>
       </c>
       <c r="B460" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C460">
         <v>103.9307</v>
@@ -6862,26 +6810,26 @@
         <v>108.9141</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A461" s="2">
+    <row r="461" spans="1:4">
+      <c r="A461" s="1">
         <v>46167</v>
       </c>
       <c r="B461" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C461">
         <v>103.9808</v>
       </c>
       <c r="D461">
-        <v>108.84350000000001</v>
-      </c>
-    </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A462" s="2">
+        <v>108.8435</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4">
+      <c r="A462" s="1">
         <v>46168</v>
       </c>
       <c r="B462" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C462">
         <v>104.4061</v>
@@ -6890,26 +6838,26 @@
         <v>107.2927</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A463" s="2">
+    <row r="463" spans="1:4">
+      <c r="A463" s="1">
         <v>46169</v>
       </c>
       <c r="B463" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C463">
-        <v>105.44370000000001</v>
+        <v>105.4437</v>
       </c>
       <c r="D463">
-        <v>108.13249999999999</v>
-      </c>
-    </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A464" s="2">
+        <v>108.1325</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4">
+      <c r="A464" s="1">
         <v>46170</v>
       </c>
       <c r="B464" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C464">
         <v>106.9062</v>
@@ -6918,26 +6866,26 @@
         <v>107.6524</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A465" s="2">
+    <row r="465" spans="1:4">
+      <c r="A465" s="1">
         <v>46171</v>
       </c>
       <c r="B465" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C465">
         <v>107.2225</v>
       </c>
       <c r="D465">
-        <v>107.23560000000001</v>
-      </c>
-    </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A466" s="2">
+        <v>107.2356</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4">
+      <c r="A466" s="1">
         <v>46174</v>
       </c>
       <c r="B466" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C466">
         <v>107.7846</v>
@@ -6946,68 +6894,68 @@
         <v>106.3608</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A467" s="2">
+    <row r="467" spans="1:4">
+      <c r="A467" s="1">
         <v>46175</v>
       </c>
       <c r="B467" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C467">
-        <v>106.81950000000001</v>
+        <v>106.8195</v>
       </c>
       <c r="D467">
         <v>105.8466</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A468" s="2">
+    <row r="468" spans="1:4">
+      <c r="A468" s="1">
         <v>46176</v>
       </c>
       <c r="B468" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C468">
-        <v>106.78919999999999</v>
+        <v>106.7892</v>
       </c>
       <c r="D468">
         <v>106.2513</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A469" s="2">
+    <row r="469" spans="1:4">
+      <c r="A469" s="1">
         <v>46177</v>
       </c>
       <c r="B469" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C469">
         <v>107.6545</v>
       </c>
       <c r="D469">
-        <v>106.13290000000001</v>
-      </c>
-    </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A470" s="2">
+        <v>106.1329</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4">
+      <c r="A470" s="1">
         <v>46178</v>
       </c>
       <c r="B470" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C470">
         <v>108.4615</v>
       </c>
       <c r="D470">
-        <v>106.45440000000001</v>
-      </c>
-    </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A471" s="2">
+        <v>106.4544</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4">
+      <c r="A471" s="1">
         <v>46181</v>
       </c>
       <c r="B471" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C471">
         <v>108.6957</v>
@@ -7016,12 +6964,12 @@
         <v>106.8052</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A472" s="2">
+    <row r="472" spans="1:4">
+      <c r="A472" s="1">
         <v>46182</v>
       </c>
       <c r="B472" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C472">
         <v>109.5287</v>
@@ -7030,12 +6978,12 @@
         <v>107.9764</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A473" s="2">
+    <row r="473" spans="1:4">
+      <c r="A473" s="1">
         <v>46183</v>
       </c>
       <c r="B473" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C473">
         <v>110.0146</v>
@@ -7044,26 +6992,26 @@
         <v>107.7235</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A474" s="2">
+    <row r="474" spans="1:4">
+      <c r="A474" s="1">
         <v>46184</v>
       </c>
       <c r="B474" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C474">
-        <v>111.13939999999999</v>
+        <v>111.1394</v>
       </c>
       <c r="D474">
-        <v>106.49379999999999</v>
-      </c>
-    </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A475" s="2">
+        <v>106.4938</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4">
+      <c r="A475" s="1">
         <v>46185</v>
       </c>
       <c r="B475" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C475">
         <v>111.4498</v>
@@ -7072,12 +7020,12 @@
         <v>107.4456</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A476" s="2">
+    <row r="476" spans="1:4">
+      <c r="A476" s="1">
         <v>46188</v>
       </c>
       <c r="B476" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C476">
         <v>111.1747</v>
@@ -7086,12 +7034,12 @@
         <v>107.2037</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A477" s="2">
+    <row r="477" spans="1:4">
+      <c r="A477" s="1">
         <v>46189</v>
       </c>
       <c r="B477" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C477">
         <v>111.5275</v>
@@ -7100,12 +7048,12 @@
         <v>108.2025</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A478" s="2">
+    <row r="478" spans="1:4">
+      <c r="A478" s="1">
         <v>46190</v>
       </c>
       <c r="B478" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C478">
         <v>108.9098</v>
@@ -7114,26 +7062,26 @@
         <v>108.5776</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A479" s="2">
+    <row r="479" spans="1:4">
+      <c r="A479" s="1">
         <v>46191</v>
       </c>
       <c r="B479" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C479">
         <v>109.2972</v>
       </c>
       <c r="D479">
-        <v>108.50709999999999</v>
-      </c>
-    </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A480" s="2">
+        <v>108.5071</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4">
+      <c r="A480" s="1">
         <v>46192</v>
       </c>
       <c r="B480" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C480">
         <v>106.092</v>
@@ -7142,12 +7090,12 @@
         <v>108.8533</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A481" s="2">
+    <row r="481" spans="1:4">
+      <c r="A481" s="1">
         <v>46195</v>
       </c>
       <c r="B481" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C481">
         <v>104.6465</v>
@@ -7156,12 +7104,12 @@
         <v>110.5958</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A482" s="2">
+    <row r="482" spans="1:4">
+      <c r="A482" s="1">
         <v>46196</v>
       </c>
       <c r="B482" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C482">
         <v>105.0775</v>
@@ -7170,26 +7118,26 @@
         <v>112.4777</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A483" s="2">
+    <row r="483" spans="1:4">
+      <c r="A483" s="1">
         <v>46197</v>
       </c>
       <c r="B483" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C483">
-        <v>105.53230000000001</v>
+        <v>105.5323</v>
       </c>
       <c r="D483">
         <v>112.5851</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A484" s="2">
+    <row r="484" spans="1:4">
+      <c r="A484" s="1">
         <v>46198</v>
       </c>
       <c r="B484" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C484">
         <v>104.5774</v>
@@ -7198,40 +7146,40 @@
         <v>112.7744</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A485" s="2">
+    <row r="485" spans="1:4">
+      <c r="A485" s="1">
         <v>46199</v>
       </c>
       <c r="B485" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C485">
         <v>104.0153</v>
       </c>
       <c r="D485">
-        <v>113.79049999999999</v>
-      </c>
-    </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A486" s="2">
+        <v>113.7905</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4">
+      <c r="A486" s="1">
         <v>46202</v>
       </c>
       <c r="B486" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C486">
         <v>105.2231</v>
       </c>
       <c r="D486">
-        <v>113.06619999999999</v>
-      </c>
-    </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A487" s="2">
+        <v>113.0662</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4">
+      <c r="A487" s="1">
         <v>46203</v>
       </c>
       <c r="B487" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C487">
         <v>104.8533</v>
@@ -7240,26 +7188,26 @@
         <v>113.4127</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A488" s="2">
+    <row r="488" spans="1:4">
+      <c r="A488" s="1">
         <v>46204</v>
       </c>
       <c r="B488" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C488">
-        <v>106.81699999999999</v>
+        <v>106.817</v>
       </c>
       <c r="D488">
         <v>113.4346</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A489" s="2">
+    <row r="489" spans="1:4">
+      <c r="A489" s="1">
         <v>46205</v>
       </c>
       <c r="B489" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C489">
         <v>106.8616</v>
@@ -7268,40 +7216,40 @@
         <v>113.7649</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A490" s="2">
+    <row r="490" spans="1:4">
+      <c r="A490" s="1">
         <v>46206</v>
       </c>
       <c r="B490" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C490">
-        <v>107.26349999999999</v>
+        <v>107.2635</v>
       </c>
       <c r="D490">
         <v>113.0519</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A491" s="2">
+    <row r="491" spans="1:4">
+      <c r="A491" s="1">
         <v>46209</v>
       </c>
       <c r="B491" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C491">
         <v>108.7246</v>
       </c>
       <c r="D491">
-        <v>111.65949999999999</v>
-      </c>
-    </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A492" s="2">
+        <v>111.6595</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4">
+      <c r="A492" s="1">
         <v>46210</v>
       </c>
       <c r="B492" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C492">
         <v>108.8879</v>
@@ -7310,12 +7258,12 @@
         <v>109.8524</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A493" s="2">
+    <row r="493" spans="1:4">
+      <c r="A493" s="1">
         <v>46211</v>
       </c>
       <c r="B493" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C493">
         <v>108.0449</v>
@@ -7324,12 +7272,12 @@
         <v>108.9144</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A494" s="2">
+    <row r="494" spans="1:4">
+      <c r="A494" s="1">
         <v>46212</v>
       </c>
       <c r="B494" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C494">
         <v>107.995</v>
@@ -7338,12 +7286,12 @@
         <v>108.5583</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A495" s="2">
+    <row r="495" spans="1:4">
+      <c r="A495" s="1">
         <v>46213</v>
       </c>
       <c r="B495" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C495">
         <v>108.0104</v>
